--- a/testplan/full_rack_testplan.xlsx
+++ b/testplan/full_rack_testplan.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Execution Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testcases'!$A$2:$L$583</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testcases'!$A$2:$L$589</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -5235,7 +5235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M583"/>
+  <dimension ref="A1:M589"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="5" min="1" max="1"/>
@@ -36745,8 +36745,320 @@
         </is>
       </c>
     </row>
+    <row r="584" ht="32" customHeight="1" s="33">
+      <c r="A584" s="7" t="inlineStr">
+        <is>
+          <t>TC-BMC-001</t>
+        </is>
+      </c>
+      <c r="B584" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C584" s="5" t="inlineStr">
+        <is>
+          <t>BMC reachable and login works: every switch and compute BMC answers Redfish at its own address (bmc:) with its bmc_user and BMC password</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H584" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+        </is>
+      </c>
+      <c r="I584" s="21" t="inlineStr">
+        <is>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
+        </is>
+      </c>
+      <c r="J584" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K584" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L584" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="32" customHeight="1" s="33">
+      <c r="A585" s="7" t="inlineStr">
+        <is>
+          <t>TC-BMC-002</t>
+        </is>
+      </c>
+      <c r="B585" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C585" s="5" t="inlineStr">
+        <is>
+          <t>BMC power state: every system the switch and compute BMCs report is powered on</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H585" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+        </is>
+      </c>
+      <c r="I585" s="21" t="inlineStr">
+        <is>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
+        </is>
+      </c>
+      <c r="J585" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K585" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L585" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="32" customHeight="1" s="33">
+      <c r="A586" s="7" t="inlineStr">
+        <is>
+          <t>TC-BMC-003</t>
+        </is>
+      </c>
+      <c r="B586" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C586" s="5" t="inlineStr">
+        <is>
+          <t>BMC health: no BMC (manager) or system reports health Critical (Warning recorded)</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H586" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+        </is>
+      </c>
+      <c r="I586" s="21" t="inlineStr">
+        <is>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
+        </is>
+      </c>
+      <c r="J586" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K586" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L586" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="32" customHeight="1" s="33">
+      <c r="A587" s="7" t="inlineStr">
+        <is>
+          <t>TC-BMC-004</t>
+        </is>
+      </c>
+      <c r="B587" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C587" s="5" t="inlineStr">
+        <is>
+          <t>BMC sensors: no temperature, fan, voltage or power-supply sensor Critical or beyond its critical limit (beyond a non-critical limit recorded)</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H587" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+        </is>
+      </c>
+      <c r="I587" s="21" t="inlineStr">
+        <is>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
+        </is>
+      </c>
+      <c r="J587" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K587" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L587" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="32" customHeight="1" s="33">
+      <c r="A588" s="7" t="inlineStr">
+        <is>
+          <t>TC-BMC-005</t>
+        </is>
+      </c>
+      <c r="B588" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C588" s="5" t="inlineStr">
+        <is>
+          <t>BMC event log: no Critical entry in the last 24 h (thresholds.bmc.log_window_h); Warning entries counted</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H588" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+        </is>
+      </c>
+      <c r="I588" s="21" t="inlineStr">
+        <is>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
+        </is>
+      </c>
+      <c r="J588" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K588" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L588" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="32" customHeight="1" s="33">
+      <c r="A589" s="7" t="inlineStr">
+        <is>
+          <t>TC-BMC-006</t>
+        </is>
+      </c>
+      <c r="B589" s="7" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C589" s="5" t="inlineStr">
+        <is>
+          <t>BMC firmware consistent: same BMC firmware version on every compute tray, and on every switch tray</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H589" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+        </is>
+      </c>
+      <c r="I589" s="21" t="inlineStr">
+        <is>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
+        </is>
+      </c>
+      <c r="J589" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K589" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L589" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L583">
+  <autoFilter ref="A2:L589">
     <filterColumn colId="3" hiddenButton="0" showButton="1">
       <filters>
         <filter val="No"/>

--- a/testplan/full_rack_testplan.xlsx
+++ b/testplan/full_rack_testplan.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Execution Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testcases'!$A$2:$L$589</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testcases'!$A$2:$L$698</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -5235,7 +5235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M589"/>
+  <dimension ref="A1:M698"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="5" min="1" max="1"/>
@@ -37057,8 +37057,5676 @@
         </is>
       </c>
     </row>
+    <row r="590" ht="32" customHeight="1" s="33">
+      <c r="A590" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.1-1</t>
+        </is>
+      </c>
+      <c r="B590" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C590" s="5" t="inlineStr">
+        <is>
+          <t>GET Service Root (Tc7.2.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H590" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I590" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J590" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K590" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L590" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="32" customHeight="1" s="33">
+      <c r="A591" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.1-2</t>
+        </is>
+      </c>
+      <c r="B591" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C591" s="5" t="inlineStr">
+        <is>
+          <t>GET OData Service Document (Tc7.2.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H591" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I591" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J591" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K591" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L591" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="32" customHeight="1" s="33">
+      <c r="A592" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.1-3</t>
+        </is>
+      </c>
+      <c r="B592" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C592" s="5" t="inlineStr">
+        <is>
+          <t>GET Schema Metadata ($metadata) (Tc7.2.1-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H592" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I592" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J592" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K592" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L592" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="32" customHeight="1" s="33">
+      <c r="A593" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.2-1</t>
+        </is>
+      </c>
+      <c r="B593" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>List Chassis Collection (Tc7.2.2-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H593" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I593" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J593" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K593" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L593" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="594" ht="32" customHeight="1" s="33">
+      <c r="A594" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.2-2</t>
+        </is>
+      </c>
+      <c r="B594" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C594" s="5" t="inlineStr">
+        <is>
+          <t>Get Chassis Detail (Tc7.2.2-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H594" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I594" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J594" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K594" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L594" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="32" customHeight="1" s="33">
+      <c r="A595" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.2-3</t>
+        </is>
+      </c>
+      <c r="B595" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>Get System Detail (Tc7.2.2-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H595" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I595" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J595" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K595" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L595" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="32" customHeight="1" s="33">
+      <c r="A596" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.3-1</t>
+        </is>
+      </c>
+      <c r="B596" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C596" s="5" t="inlineStr">
+        <is>
+          <t>List All Sensors (Tc7.2.3-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H596" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I596" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J596" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K596" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L596" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="32" customHeight="1" s="33">
+      <c r="A597" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.3-2</t>
+        </is>
+      </c>
+      <c r="B597" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C597" s="5" t="inlineStr">
+        <is>
+          <t>Get Individual Sensor (LeakDetector_0) (Tc7.2.3-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H597" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I597" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J597" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K597" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L597" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="32" customHeight="1" s="33">
+      <c r="A598" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.3-3</t>
+        </is>
+      </c>
+      <c r="B598" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C598" s="5" t="inlineStr">
+        <is>
+          <t>Legacy Thermal View (Tc7.2.3-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H598" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I598" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J598" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K598" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L598" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="32" customHeight="1" s="33">
+      <c r="A599" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.4-1</t>
+        </is>
+      </c>
+      <c r="B599" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C599" s="5" t="inlineStr">
+        <is>
+          <t>LeakDetection Resource (Tc7.2.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H599" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I599" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J599" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K599" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L599" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="32" customHeight="1" s="33">
+      <c r="A600" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.4-2</t>
+        </is>
+      </c>
+      <c r="B600" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C600" s="5" t="inlineStr">
+        <is>
+          <t>List LeakDetectors (Tc7.2.4-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H600" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I600" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J600" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K600" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L600" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="32" customHeight="1" s="33">
+      <c r="A601" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.4-3</t>
+        </is>
+      </c>
+      <c r="B601" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C601" s="5" t="inlineStr">
+        <is>
+          <t>LeakDetector Detail (Tc7.2.4-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H601" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I601" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J601" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K601" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L601" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="32" customHeight="1" s="33">
+      <c r="A602" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.5-1</t>
+        </is>
+      </c>
+      <c r="B602" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C602" s="5" t="inlineStr">
+        <is>
+          <t>ThermalSubsystem Overview (Tc7.2.5-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H602" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.5-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I602" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J602" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K602" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L602" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="32" customHeight="1" s="33">
+      <c r="A603" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.6-1</t>
+        </is>
+      </c>
+      <c r="B603" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C603" s="5" t="inlineStr">
+        <is>
+          <t>BMC Detail (Tc7.2.6-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H603" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I603" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J603" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K603" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L603" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="604" ht="32" customHeight="1" s="33">
+      <c r="A604" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.6-2</t>
+        </is>
+      </c>
+      <c r="B604" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C604" s="5" t="inlineStr">
+        <is>
+          <t>NetworkProtocol (Tc7.2.6-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H604" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I604" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J604" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K604" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L604" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="605" ht="32" customHeight="1" s="33">
+      <c r="A605" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.7-1</t>
+        </is>
+      </c>
+      <c r="B605" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C605" s="5" t="inlineStr">
+        <is>
+          <t>List Users (Tc7.2.7-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H605" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.7-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I605" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J605" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K605" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L605" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" ht="32" customHeight="1" s="33">
+      <c r="A606" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.7-7</t>
+        </is>
+      </c>
+      <c r="B606" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C606" s="5" t="inlineStr">
+        <is>
+          <t>List Roles (Tc7.2.7-7, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H606" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.7-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I606" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J606" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K606" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L606" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="32" customHeight="1" s="33">
+      <c r="A607" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.8-3</t>
+        </is>
+      </c>
+      <c r="B607" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C607" s="5" t="inlineStr">
+        <is>
+          <t>List Sessions (Tc7.2.8-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H607" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.8-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I607" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J607" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K607" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L607" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="32" customHeight="1" s="33">
+      <c r="A608" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.9-1</t>
+        </is>
+      </c>
+      <c r="B608" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C608" s="5" t="inlineStr">
+        <is>
+          <t>EventService Status (Tc7.2.9-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H608" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I608" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J608" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K608" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L608" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="32" customHeight="1" s="33">
+      <c r="A609" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.9-14</t>
+        </is>
+      </c>
+      <c r="B609" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C609" s="5" t="inlineStr">
+        <is>
+          <t>Verify Chassis and Sensor URIs (Native Local - No Rewriting) (Tc7.2.9-14, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H609" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I609" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J609" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K609" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L609" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="32" customHeight="1" s="33">
+      <c r="A610" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.9-18</t>
+        </is>
+      </c>
+      <c r="B610" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C610" s="5" t="inlineStr">
+        <is>
+          <t>Check Switch Manager / BMC Info (Tc7.2.9-18, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H610" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-18); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I610" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J610" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K610" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L610" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="32" customHeight="1" s="33">
+      <c r="A611" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.10-1</t>
+        </is>
+      </c>
+      <c r="B611" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C611" s="5" t="inlineStr">
+        <is>
+          <t>LogService Accessible on Switch BMC (Tc7.2.10-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H611" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I611" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J611" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K611" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L611" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="32" customHeight="1" s="33">
+      <c r="A612" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.10-13</t>
+        </is>
+      </c>
+      <c r="B612" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C612" s="5" t="inlineStr">
+        <is>
+          <t>MaxNumberOfRecords = 10,000 (Tc7.2.10-13, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H612" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I612" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J612" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K612" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L612" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="32" customHeight="1" s="33">
+      <c r="A613" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.10-14</t>
+        </is>
+      </c>
+      <c r="B613" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C613" s="5" t="inlineStr">
+        <is>
+          <t>OverWritePolicy = "WrapsWhenFull" (Tc7.2.10-14, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H613" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I613" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J613" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K613" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L613" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="32" customHeight="1" s="33">
+      <c r="A614" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.10-15</t>
+        </is>
+      </c>
+      <c r="B614" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C614" s="5" t="inlineStr">
+        <is>
+          <t>ClearLog Action Supported (Tc7.2.10-15, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H614" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-15); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I614" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J614" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K614" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L614" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="32" customHeight="1" s="33">
+      <c r="A615" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.10-18</t>
+        </is>
+      </c>
+      <c r="B615" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C615" s="5" t="inlineStr">
+        <is>
+          <t>All Three Table 37 Parameters Present Together (Tc7.2.10-18, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H615" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-18); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I615" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J615" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K615" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L615" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="616" ht="32" customHeight="1" s="33">
+      <c r="A616" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.11-1</t>
+        </is>
+      </c>
+      <c r="B616" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C616" s="5" t="inlineStr">
+        <is>
+          <t>UpdateService Overview (Tc7.2.11-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H616" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.11-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I616" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J616" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K616" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L616" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="32" customHeight="1" s="33">
+      <c r="A617" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.11-2</t>
+        </is>
+      </c>
+      <c r="B617" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C617" s="5" t="inlineStr">
+        <is>
+          <t>Firmware Inventory (Tc7.2.11-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H617" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.11-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I617" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J617" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K617" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L617" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="32" customHeight="1" s="33">
+      <c r="A618" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.4-1</t>
+        </is>
+      </c>
+      <c r="B618" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C618" s="5" t="inlineStr">
+        <is>
+          <t>GET UpdateService - Configuration (Tc7.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H618" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I618" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J618" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K618" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L618" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="32" customHeight="1" s="33">
+      <c r="A619" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.4-2</t>
+        </is>
+      </c>
+      <c r="B619" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C619" s="5" t="inlineStr">
+        <is>
+          <t>GET FirmwareInventory - Switch Collection (Tc7.4-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H619" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I619" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J619" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K619" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L619" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="32" customHeight="1" s="33">
+      <c r="A620" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.4-6</t>
+        </is>
+      </c>
+      <c r="B620" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C620" s="5" t="inlineStr">
+        <is>
+          <t>GET FirmwareInventory/{id} - Individual Entry (Tc7.4-6, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H620" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I620" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J620" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K620" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L620" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="32" customHeight="1" s="33">
+      <c r="A621" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.4-7</t>
+        </is>
+      </c>
+      <c r="B621" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C621" s="5" t="inlineStr">
+        <is>
+          <t>Verify Switch Firmware Component IDs (Tc7.4-7, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H621" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I621" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J621" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K621" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L621" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="32" customHeight="1" s="33">
+      <c r="A622" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.4-8</t>
+        </is>
+      </c>
+      <c r="B622" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C622" s="5" t="inlineStr">
+        <is>
+          <t>Verify All Entries Accessible (Tc7.4-8, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H622" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I622" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J622" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K622" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L622" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="623" ht="32" customHeight="1" s="33">
+      <c r="A623" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.4-11</t>
+        </is>
+      </c>
+      <c r="B623" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C623" s="5" t="inlineStr">
+        <is>
+          <t>Verify Switch BMC Firmware Entry (Tc7.4-11, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H623" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-11); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I623" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J623" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K623" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L623" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="624" ht="32" customHeight="1" s="33">
+      <c r="A624" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.12-1</t>
+        </is>
+      </c>
+      <c r="B624" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C624" s="5" t="inlineStr">
+        <is>
+          <t>List Ethernet Interfaces (Tc7.2.12-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H624" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.12-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I624" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J624" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K624" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L624" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="625" ht="32" customHeight="1" s="33">
+      <c r="A625" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.12-2</t>
+        </is>
+      </c>
+      <c r="B625" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C625" s="5" t="inlineStr">
+        <is>
+          <t>Get eth0 Details (Tc7.2.12-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H625" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.12-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I625" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J625" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K625" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L625" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="626" ht="32" customHeight="1" s="33">
+      <c r="A626" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.13-1</t>
+        </is>
+      </c>
+      <c r="B626" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C626" s="5" t="inlineStr">
+        <is>
+          <t>CertificateService Root (Tc7.2.13-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H626" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I626" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J626" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K626" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L626" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="627" ht="32" customHeight="1" s="33">
+      <c r="A627" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.13-2</t>
+        </is>
+      </c>
+      <c r="B627" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C627" s="5" t="inlineStr">
+        <is>
+          <t>HTTPS Certificates (Tc7.2.13-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H627" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I627" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J627" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K627" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L627" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="628" ht="32" customHeight="1" s="33">
+      <c r="A628" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.13-3</t>
+        </is>
+      </c>
+      <c r="B628" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C628" s="5" t="inlineStr">
+        <is>
+          <t>GET Individual Certificate - Active TLS Certificate (Tc7.2.13-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H628" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I628" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J628" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K628" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L628" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="629" ht="32" customHeight="1" s="33">
+      <c r="A629" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.13-6</t>
+        </is>
+      </c>
+      <c r="B629" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C629" s="5" t="inlineStr">
+        <is>
+          <t>Verify ReplaceCertificate Action Target URI Format (Tc7.2.13-6, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H629" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I629" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J629" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K629" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L629" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="630" ht="32" customHeight="1" s="33">
+      <c r="A630" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.13-7</t>
+        </is>
+      </c>
+      <c r="B630" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C630" s="5" t="inlineStr">
+        <is>
+          <t>Verify Certificate Validity Period (Tc7.2.13-7, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H630" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I630" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J630" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K630" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L630" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="631" ht="32" customHeight="1" s="33">
+      <c r="A631" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-1</t>
+        </is>
+      </c>
+      <c r="B631" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C631" s="5" t="inlineStr">
+        <is>
+          <t>GET TaskService - Configuration (Tc7.2.14-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H631" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I631" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J631" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K631" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L631" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="32" customHeight="1" s="33">
+      <c r="A632" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-2</t>
+        </is>
+      </c>
+      <c r="B632" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C632" s="5" t="inlineStr">
+        <is>
+          <t>GET Tasks Collection (Tc7.2.14-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H632" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I632" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J632" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K632" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L632" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="32" customHeight="1" s="33">
+      <c r="A633" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-3</t>
+        </is>
+      </c>
+      <c r="B633" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C633" s="5" t="inlineStr">
+        <is>
+          <t>GET Individual Task - Required Fields (Tc7.2.14-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H633" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I633" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J633" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K633" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L633" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="634" ht="32" customHeight="1" s="33">
+      <c r="A634" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-6</t>
+        </is>
+      </c>
+      <c r="B634" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C634" s="5" t="inlineStr">
+        <is>
+          <t>Task StartTime and EndTime Fields (Tc7.2.14-6, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H634" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I634" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J634" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K634" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L634" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="635" ht="32" customHeight="1" s="33">
+      <c r="A635" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-8</t>
+        </is>
+      </c>
+      <c r="B635" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C635" s="5" t="inlineStr">
+        <is>
+          <t>Task Messages Array Content (Tc7.2.14-8, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H635" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I635" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J635" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K635" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L635" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="32" customHeight="1" s="33">
+      <c r="A636" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-9</t>
+        </is>
+      </c>
+      <c r="B636" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C636" s="5" t="inlineStr">
+        <is>
+          <t>GET TelemetryService - Configuration (Tc7.2.14-9, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H636" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-9); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I636" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J636" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K636" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L636" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="32" customHeight="1" s="33">
+      <c r="A637" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-11</t>
+        </is>
+      </c>
+      <c r="B637" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C637" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricDefinitions - Collection (Tc7.2.14-11, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H637" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-11); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I637" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J637" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K637" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L637" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="638" ht="32" customHeight="1" s="33">
+      <c r="A638" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-12</t>
+        </is>
+      </c>
+      <c r="B638" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C638" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricDefinitions/{id} - Individual Definition (Tc7.2.14-12, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H638" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-12); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I638" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J638" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K638" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L638" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="639" ht="32" customHeight="1" s="33">
+      <c r="A639" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-13</t>
+        </is>
+      </c>
+      <c r="B639" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C639" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricReportDefinitions - Collection (Tc7.2.14-13, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H639" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I639" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J639" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K639" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L639" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="640" ht="32" customHeight="1" s="33">
+      <c r="A640" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-16</t>
+        </is>
+      </c>
+      <c r="B640" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C640" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricReports - Collection (Tc7.2.14-16, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H640" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-16); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I640" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J640" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K640" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L640" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="641" ht="32" customHeight="1" s="33">
+      <c r="A641" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-17</t>
+        </is>
+      </c>
+      <c r="B641" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C641" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricReports/{id} - Individual Report (Tc7.2.14-17, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H641" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-17); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I641" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J641" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K641" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L641" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="642" ht="32" customHeight="1" s="33">
+      <c r="A642" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-19</t>
+        </is>
+      </c>
+      <c r="B642" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C642" s="5" t="inlineStr">
+        <is>
+          <t>TelemetryService Structure Verified (Tc7.2.14-19, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H642" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-19); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I642" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J642" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K642" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L642" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="643" ht="32" customHeight="1" s="33">
+      <c r="A643" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-20</t>
+        </is>
+      </c>
+      <c r="B643" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C643" s="5" t="inlineStr">
+        <is>
+          <t>MetricDefinitions Auto-Populated (Tc7.2.14-20, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H643" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-20); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I643" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J643" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K643" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L643" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="644" ht="32" customHeight="1" s="33">
+      <c r="A644" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-21</t>
+        </is>
+      </c>
+      <c r="B644" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C644" s="5" t="inlineStr">
+        <is>
+          <t>Deduplication Keys Present (Tc7.2.14-21, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H644" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-21); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I644" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J644" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K644" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L644" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="645" ht="32" customHeight="1" s="33">
+      <c r="A645" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-22</t>
+        </is>
+      </c>
+      <c r="B645" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C645" s="5" t="inlineStr">
+        <is>
+          <t>MetricProperties Lists Switch Sensor URIs (Tc7.2.14-22, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H645" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-22); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I645" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J645" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K645" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L645" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="646" ht="32" customHeight="1" s="33">
+      <c r="A646" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.14-23</t>
+        </is>
+      </c>
+      <c r="B646" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C646" s="5" t="inlineStr">
+        <is>
+          <t>Client Workflow - Browse (Tc7.2.14-23, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H646" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-23); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I646" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J646" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K646" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L646" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="647" ht="32" customHeight="1" s="33">
+      <c r="A647" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-4</t>
+        </is>
+      </c>
+      <c r="B647" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C647" s="5" t="inlineStr">
+        <is>
+          <t>TelemetryService Structure Verified (Tc7.5.9-4, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H647" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-4); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I647" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J647" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K647" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L647" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="648" ht="32" customHeight="1" s="33">
+      <c r="A648" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-5</t>
+        </is>
+      </c>
+      <c r="B648" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C648" s="5" t="inlineStr">
+        <is>
+          <t>Deduplication Keys Present (Tc7.5.9-5, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H648" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-5); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I648" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J648" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K648" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L648" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="649" ht="32" customHeight="1" s="33">
+      <c r="A649" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-6</t>
+        </is>
+      </c>
+      <c r="B649" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C649" s="5" t="inlineStr">
+        <is>
+          <t>MetricProperties Lists Switch Sensor URIs (Tc7.5.9-6, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H649" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I649" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J649" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K649" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L649" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="32" customHeight="1" s="33">
+      <c r="A650" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-7</t>
+        </is>
+      </c>
+      <c r="B650" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C650" s="5" t="inlineStr">
+        <is>
+          <t>Client Workflow - Browse (Tc7.5.9-7, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H650" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I650" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J650" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K650" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L650" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="651" ht="32" customHeight="1" s="33">
+      <c r="A651" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-8</t>
+        </is>
+      </c>
+      <c r="B651" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C651" s="5" t="inlineStr">
+        <is>
+          <t>Client Workflow - Pick and Review MetricProperties (Tc7.5.9-8, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H651" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I651" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J651" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K651" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L651" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="652" ht="32" customHeight="1" s="33">
+      <c r="A652" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-13</t>
+        </is>
+      </c>
+      <c r="B652" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C652" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricReports - Collection (Tc7.5.9-13, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H652" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I652" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J652" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K652" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L652" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="653" ht="32" customHeight="1" s="33">
+      <c r="A653" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-14</t>
+        </is>
+      </c>
+      <c r="B653" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C653" s="5" t="inlineStr">
+        <is>
+          <t>GET MetricReports/{id} (Tc7.5.9-14, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H653" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I653" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J653" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K653" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L653" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="654" ht="32" customHeight="1" s="33">
+      <c r="A654" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.1-1</t>
+        </is>
+      </c>
+      <c r="B654" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C654" s="5" t="inlineStr">
+        <is>
+          <t>Service Root &amp; Version (Tc7.3.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H654" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I654" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J654" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K654" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L654" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="655" ht="32" customHeight="1" s="33">
+      <c r="A655" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.1-2</t>
+        </is>
+      </c>
+      <c r="B655" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C655" s="5" t="inlineStr">
+        <is>
+          <t>Managers &amp; NetworkProtocol (Tc7.3.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H655" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I655" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J655" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K655" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L655" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="656" ht="32" customHeight="1" s="33">
+      <c r="A656" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.1-3</t>
+        </is>
+      </c>
+      <c r="B656" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C656" s="5" t="inlineStr">
+        <is>
+          <t>EthernetInterfaces (eth0) (Tc7.3.1-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H656" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I656" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J656" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K656" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L656" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="657" ht="32" customHeight="1" s="33">
+      <c r="A657" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.4-1</t>
+        </is>
+      </c>
+      <c r="B657" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C657" s="5" t="inlineStr">
+        <is>
+          <t>Journal &amp; SEL LogServices (Tc7.3.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H657" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I657" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J657" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K657" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L657" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="658" ht="32" customHeight="1" s="33">
+      <c r="A658" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.5-1</t>
+        </is>
+      </c>
+      <c r="B658" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C658" s="5" t="inlineStr">
+        <is>
+          <t>Authentication &amp; TLS Enforcement (Tc7.3.5-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H658" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.5-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I658" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J658" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K658" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L658" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="659" ht="32" customHeight="1" s="33">
+      <c r="A659" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.6-1</t>
+        </is>
+      </c>
+      <c r="B659" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C659" s="5" t="inlineStr">
+        <is>
+          <t>Sensor Discovery (D-Bus &amp; Redfish) (Tc7.3.6-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H659" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.6-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I659" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J659" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K659" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L659" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="660" ht="32" customHeight="1" s="33">
+      <c r="A660" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.3.6-2</t>
+        </is>
+      </c>
+      <c r="B660" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C660" s="5" t="inlineStr">
+        <is>
+          <t>Threshold &amp; Health Mapping (Tc7.3.6-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H660" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.6-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I660" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J660" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K660" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L660" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="661" ht="32" customHeight="1" s="33">
+      <c r="A661" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.13-1</t>
+        </is>
+      </c>
+      <c r="B661" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C661" s="5" t="inlineStr">
+        <is>
+          <t>GET ServiceConditions - Root Resource (Tc7.5.13-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H661" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I661" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J661" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K661" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L661" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="662" ht="32" customHeight="1" s="33">
+      <c r="A662" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.13-2</t>
+        </is>
+      </c>
+      <c r="B662" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C662" s="5" t="inlineStr">
+        <is>
+          <t>Verify Condition Object Structure (Tc7.5.13-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H662" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I662" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J662" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K662" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L662" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="663" ht="32" customHeight="1" s="33">
+      <c r="A663" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.13-3</t>
+        </is>
+      </c>
+      <c r="B663" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C663" s="5" t="inlineStr">
+        <is>
+          <t>Verify Severity Values (Tc7.5.13-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H663" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I663" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J663" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K663" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L663" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="664" ht="32" customHeight="1" s="33">
+      <c r="A664" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.13-4</t>
+        </is>
+      </c>
+      <c r="B664" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C664" s="5" t="inlineStr">
+        <is>
+          <t>Verify OriginOfCondition URIs (Tc7.5.13-4, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H664" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-4); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I664" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J664" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K664" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L664" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="665" ht="32" customHeight="1" s="33">
+      <c r="A665" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.13-5</t>
+        </is>
+      </c>
+      <c r="B665" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C665" s="5" t="inlineStr">
+        <is>
+          <t>Verify Timestamp Format (Tc7.5.13-5, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H665" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-5); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I665" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J665" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K665" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L665" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="666" ht="32" customHeight="1" s="33">
+      <c r="A666" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.13-7</t>
+        </is>
+      </c>
+      <c r="B666" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C666" s="5" t="inlineStr">
+        <is>
+          <t>Client Workflow - Poll, Identify, Filter (Tc7.5.13-7, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H666" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+        </is>
+      </c>
+      <c r="I666" s="21" t="inlineStr">
+        <is>
+          <t>Switch BMC Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J666" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K666" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L666" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="667" ht="32" customHeight="1" s="33">
+      <c r="A667" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-1</t>
+        </is>
+      </c>
+      <c r="B667" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C667" s="5" t="inlineStr">
+        <is>
+          <t>USB Presence Detection ['check'] (Tc7.1.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H667" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I667" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J667" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K667" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L667" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="668" ht="32" customHeight="1" s="33">
+      <c r="A668" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-2</t>
+        </is>
+      </c>
+      <c r="B668" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C668" s="5" t="inlineStr">
+        <is>
+          <t>Help Menu ['--help' | '-h'] (Tc7.1.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H668" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-2); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I668" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J668" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K668" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L668" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="669" ht="32" customHeight="1" s="33">
+      <c r="A669" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-4</t>
+        </is>
+      </c>
+      <c r="B669" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C669" s="5" t="inlineStr">
+        <is>
+          <t>Display Version Information ['version'] (Tc7.1.1-4, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H669" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-4); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I669" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J669" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K669" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L669" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="670" ht="32" customHeight="1" s="33">
+      <c r="A670" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-5</t>
+        </is>
+      </c>
+      <c r="B670" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C670" s="5" t="inlineStr">
+        <is>
+          <t>System Status Overview ['status'] (Tc7.1.1-5, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H670" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-5); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I670" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J670" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K670" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L670" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="671" ht="32" customHeight="1" s="33">
+      <c r="A671" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-6</t>
+        </is>
+      </c>
+      <c r="B671" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C671" s="5" t="inlineStr">
+        <is>
+          <t>Health Check ['health'] (Tc7.1.1-6, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H671" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-6); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I671" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J671" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K671" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L671" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="672" ht="32" customHeight="1" s="33">
+      <c r="A672" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-9</t>
+        </is>
+      </c>
+      <c r="B672" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C672" s="5" t="inlineStr">
+        <is>
+          <t>Default Boot Flash ('flash-info') (Tc7.1.1-9, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H672" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-9); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I672" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J672" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K672" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L672" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="673" ht="32" customHeight="1" s="33">
+      <c r="A673" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.1-10</t>
+        </is>
+      </c>
+      <c r="B673" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C673" s="5" t="inlineStr">
+        <is>
+          <t>Flash Partition Information ['flash-info'] (Tc7.1.1-10, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H673" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-10); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I673" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J673" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K673" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L673" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="674" ht="32" customHeight="1" s="33">
+      <c r="A674" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.2-1</t>
+        </is>
+      </c>
+      <c r="B674" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C674" s="5" t="inlineStr">
+        <is>
+          <t>Journal Streaming [No Filter |errors |warnings |boot |] (Tc7.1.2-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H674" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.2-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I674" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J674" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K674" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L674" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="675" ht="32" customHeight="1" s="33">
+      <c r="A675" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.2-2</t>
+        </is>
+      </c>
+      <c r="B675" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C675" s="5" t="inlineStr">
+        <is>
+          <t>Kernel Logs ['dmesg'] (Tc7.1.2-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H675" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.2-2); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I675" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J675" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K675" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L675" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="676" ht="32" customHeight="1" s="33">
+      <c r="A676" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.3-3</t>
+        </is>
+      </c>
+      <c r="B676" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C676" s="5" t="inlineStr">
+        <is>
+          <t>Check SSH Access Status ['ssh-access status'] (Tc7.1.3-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H676" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.3-3); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I676" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J676" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K676" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L676" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="677" ht="32" customHeight="1" s="33">
+      <c r="A677" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.1.4-1</t>
+        </is>
+      </c>
+      <c r="B677" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C677" s="5" t="inlineStr">
+        <is>
+          <t>List Configuration Files ['config-list'] (Tc7.1.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H677" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.4-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I677" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J677" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K677" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L677" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="678" ht="32" customHeight="1" s="33">
+      <c r="A678" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.6-17</t>
+        </is>
+      </c>
+      <c r="B678" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C678" s="5" t="inlineStr">
+        <is>
+          <t>Verify redfish docker container is only enabled on liquid cooling platforms. (Tc7.2.6-17, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H678" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-17); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I678" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J678" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K678" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L678" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="679" ht="32" customHeight="1" s="33">
+      <c r="A679" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.2.6-19</t>
+        </is>
+      </c>
+      <c r="B679" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C679" s="5" t="inlineStr">
+        <is>
+          <t>Rack Manager Reachability - REACHABLE (Tc7.2.6-19, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H679" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-19); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+        </is>
+      </c>
+      <c r="I679" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+        </is>
+      </c>
+      <c r="J679" s="21" t="inlineStr">
+        <is>
+          <t>BMC (Switch)</t>
+        </is>
+      </c>
+      <c r="K679" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L679" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="680" ht="32" customHeight="1" s="33">
+      <c r="A680" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.1-1</t>
+        </is>
+      </c>
+      <c r="B680" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C680" s="5" t="inlineStr">
+        <is>
+          <t>GET Aggregator Service Root (Tc7.5.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H680" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I680" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J680" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K680" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L680" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="681" ht="32" customHeight="1" s="33">
+      <c r="A681" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.1-2</t>
+        </is>
+      </c>
+      <c r="B681" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C681" s="5" t="inlineStr">
+        <is>
+          <t>GET /redfish Version Object (Tc7.5.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H681" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I681" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J681" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K681" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L681" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="682" ht="32" customHeight="1" s="33">
+      <c r="A682" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.1-3</t>
+        </is>
+      </c>
+      <c r="B682" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C682" s="5" t="inlineStr">
+        <is>
+          <t>GET JsonSchemas Collection (Tc7.5.1-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H682" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I682" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J682" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K682" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L682" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="683" ht="32" customHeight="1" s="33">
+      <c r="A683" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.1-4</t>
+        </is>
+      </c>
+      <c r="B683" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C683" s="5" t="inlineStr">
+        <is>
+          <t>GET Registries Collection (Tc7.5.1-4, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H683" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I683" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J683" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K683" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L683" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="684" ht="32" customHeight="1" s="33">
+      <c r="A684" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.2-4</t>
+        </is>
+      </c>
+      <c r="B684" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C684" s="5" t="inlineStr">
+        <is>
+          <t>List Connection Methods (Tc7.5.2-4, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H684" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.2-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I684" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J684" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K684" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L684" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="685" ht="32" customHeight="1" s="33">
+      <c r="A685" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.3-1</t>
+        </is>
+      </c>
+      <c r="B685" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C685" s="5" t="inlineStr">
+        <is>
+          <t>Verify Transparent Proxy Rule (Tc7.5.3-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H685" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.3-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I685" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J685" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K685" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L685" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="686" ht="32" customHeight="1" s="33">
+      <c r="A686" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.3-2</t>
+        </is>
+      </c>
+      <c r="B686" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C686" s="5" t="inlineStr">
+        <is>
+          <t>Verify URI Rewriting in Responses (Tc7.5.3-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H686" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.3-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I686" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J686" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K686" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L686" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="687" ht="32" customHeight="1" s="33">
+      <c r="A687" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.4-1</t>
+        </is>
+      </c>
+      <c r="B687" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C687" s="5" t="inlineStr">
+        <is>
+          <t>Systems Collection Membership (Tc7.5.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H687" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I687" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J687" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K687" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L687" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="688" ht="32" customHeight="1" s="33">
+      <c r="A688" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.4-2</t>
+        </is>
+      </c>
+      <c r="B688" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C688" s="5" t="inlineStr">
+        <is>
+          <t>Chassis Collection Membership (Tc7.5.4-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H688" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I688" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J688" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K688" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L688" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="689" ht="32" customHeight="1" s="33">
+      <c r="A689" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.4-3</t>
+        </is>
+      </c>
+      <c r="B689" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C689" s="5" t="inlineStr">
+        <is>
+          <t>Managers Collection Membership (Tc7.5.4-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H689" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I689" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J689" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K689" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L689" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="690" ht="32" customHeight="1" s="33">
+      <c r="A690" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.4-4</t>
+        </is>
+      </c>
+      <c r="B690" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C690" s="5" t="inlineStr">
+        <is>
+          <t>Chassis Containment Hierarchy (Tc7.5.4-4, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H690" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I690" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J690" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K690" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L690" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="691" ht="32" customHeight="1" s="33">
+      <c r="A691" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.5-1</t>
+        </is>
+      </c>
+      <c r="B691" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C691" s="5" t="inlineStr">
+        <is>
+          <t>ComponentIntegrity Collection (Tc7.5.5-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H691" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.5-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I691" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J691" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K691" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L691" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="692" ht="32" customHeight="1" s="33">
+      <c r="A692" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.7-1</t>
+        </is>
+      </c>
+      <c r="B692" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C692" s="5" t="inlineStr">
+        <is>
+          <t>PowerEquipment Singleton (Tc7.5.7-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H692" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I692" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J692" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K692" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L692" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="693" ht="32" customHeight="1" s="33">
+      <c r="A693" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.7-2</t>
+        </is>
+      </c>
+      <c r="B693" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C693" s="5" t="inlineStr">
+        <is>
+          <t>Power Shelf Sub-Resources (Tc7.5.7-2, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H693" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I693" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J693" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K693" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L693" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="694" ht="32" customHeight="1" s="33">
+      <c r="A694" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.7-3</t>
+        </is>
+      </c>
+      <c r="B694" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C694" s="5" t="inlineStr">
+        <is>
+          <t>Super Cap Battery Resources (Tc7.5.7-3, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H694" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I694" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J694" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K694" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L694" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="695" ht="32" customHeight="1" s="33">
+      <c r="A695" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.8-1</t>
+        </is>
+      </c>
+      <c r="B695" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C695" s="5" t="inlineStr">
+        <is>
+          <t>EventService Configuration (Tc7.5.8-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H695" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.8-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I695" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J695" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K695" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L695" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="696" ht="32" customHeight="1" s="33">
+      <c r="A696" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.9-1</t>
+        </is>
+      </c>
+      <c r="B696" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C696" s="5" t="inlineStr">
+        <is>
+          <t>Deduplicated MetricDefinitions (Tc7.5.9-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H696" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I696" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J696" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K696" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L696" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="697" ht="32" customHeight="1" s="33">
+      <c r="A697" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.10-1</t>
+        </is>
+      </c>
+      <c r="B697" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C697" s="5" t="inlineStr">
+        <is>
+          <t>Task Tracking for Async Operations (Tc7.5.10-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H697" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.10-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I697" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J697" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K697" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L697" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" ht="32" customHeight="1" s="33">
+      <c r="A698" s="7" t="inlineStr">
+        <is>
+          <t>TC-BLT-7.5.11-1</t>
+        </is>
+      </c>
+      <c r="B698" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C698" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated FirmwareInventory (Tc7.5.11-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H698" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.11-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I698" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J698" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K698" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L698" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L589">
+  <autoFilter ref="A2:L698">
     <filterColumn colId="3" hiddenButton="0" showButton="1">
       <filters>
         <filter val="No"/>

--- a/testplan/full_rack_testplan.xlsx
+++ b/testplan/full_rack_testplan.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Execution Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testcases'!$A$2:$L$698</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testcases'!$A$2:$L$699</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -5235,7 +5235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M698"/>
+  <dimension ref="A1:M699"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="5" min="1" max="1"/>
@@ -35562,112 +35562,113 @@
       </c>
       <c r="M562" s="21" t="n"/>
     </row>
-    <row r="563" hidden="1" ht="96" customHeight="1" s="33">
+    <row r="563" hidden="1" ht="80" customHeight="1" s="33">
       <c r="A563" s="7" t="inlineStr">
         <is>
+          <t>TC-SWH-063</t>
+        </is>
+      </c>
+      <c r="B563" s="7" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>PFC lossless configuration complete: lossless PG headroom, ECN marking and PFC watchdog on every pfc_enable priority, every dot1p mapped, lossy classes not on lossless buffers, no threshold above its pool</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>SONiC.202505I20261010141343.2 (blantons-mr3-sw)</t>
+        </is>
+      </c>
+      <c r="H563" s="21" t="inlineStr">
+        <is>
+          <t>[blantons-mr3-sw (MR3, QFX5252), read-only, 20 Oct 2026, helios-tests mr3-20261020-193359] FAIL: the same 6 findings on each ASIC (256 ports each, pfc_enable 0,1): (1) no PFC watchdog - a PFC storm or deadlock is not detected or broken; (2) no ECN / WRED on lossless queues 0,1 - no DCQCN / CNP, congestion handled by PFC pause alone; (3) dot1p 2-6 not mapped in IFOE_TC_MAP - those frames fall back to TC0, which is lossless; (4) lossy TC7 on egress queue 7 with q_lossless_profile (strict priority) although priority 7 has no PFC; (5) PG7 has no ingress buffer (no BUFFER_PG, no lossy pool) - relies on the ASIC default; (6) q_lossless_profile static_th 265332900 B above the egress_pool size 259953960 B - no per-queue limit. Not yet run on g02-g17.
+Earlier: Added to the test plan by helios-tests on 20 Oct 2026 (not in BKC-26.12). Completes TC-SWH-046 (which only checks that ports agree and no storm): it judges whether the lossless setup itself is complete.</t>
+        </is>
+      </c>
+      <c r="I563" s="21" t="inlineStr">
+        <is>
+          <t>Switch SSH</t>
+        </is>
+      </c>
+      <c r="J563" s="21" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="K563" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L563" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" hidden="1" ht="96" customHeight="1" s="33">
+      <c r="A564" s="7" t="inlineStr">
+        <is>
           <t>HC-000</t>
         </is>
       </c>
-      <c r="B563" s="7" t="inlineStr">
+      <c r="B564" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C563" s="5" t="inlineStr">
+      <c r="C564" s="5" t="inlineStr">
         <is>
           <t>Health check: AFM rack state (cluster, switch / compute admission and health, system vPOD, pending operations) + baseline snapshot</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr">
+      <c r="G564" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H563" s="21" t="inlineStr">
+      <c r="H564" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:23 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
         </is>
       </c>
-      <c r="I563" s="21" t="inlineStr">
+      <c r="I564" s="21" t="inlineStr">
         <is>
           <t>AFM API + switch SSH</t>
         </is>
       </c>
-      <c r="J563" s="21" t="inlineStr">
+      <c r="J564" s="21" t="inlineStr">
         <is>
           <t>Health check (Switch + Compute, AFM API)</t>
-        </is>
-      </c>
-      <c r="K563" s="21" t="inlineStr">
-        <is>
-          <t>Added - helios-tests (15 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="L563" s="21" t="inlineStr">
-        <is>
-          <t>Non-disruptive</t>
-        </is>
-      </c>
-      <c r="M563" t="inlineStr">
-        <is>
-          <t>Blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="564" hidden="1" ht="112" customHeight="1" s="33">
-      <c r="A564" s="7" t="inlineStr">
-        <is>
-          <t>HC-001</t>
-        </is>
-      </c>
-      <c r="B564" s="7" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C564" s="5" t="inlineStr">
-        <is>
-          <t>Health check: every switch and compute tray answers SSH</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
-        </is>
-      </c>
-      <c r="H564" s="21" t="inlineStr">
-        <is>
-          <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
-        </is>
-      </c>
-      <c r="I564" s="21" t="inlineStr">
-        <is>
-          <t>Switch + compute SSH</t>
-        </is>
-      </c>
-      <c r="J564" s="21" t="inlineStr">
-        <is>
-          <t>Health check (Switch + Compute)</t>
         </is>
       </c>
       <c r="K564" s="21" t="inlineStr">
@@ -35689,476 +35690,476 @@
     <row r="565" hidden="1" ht="112" customHeight="1" s="33">
       <c r="A565" s="7" t="inlineStr">
         <is>
+          <t>HC-001</t>
+        </is>
+      </c>
+      <c r="B565" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>Health check: every switch and compute tray answers SSH</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
+        </is>
+      </c>
+      <c r="H565" s="21" t="inlineStr">
+        <is>
+          <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
+        </is>
+      </c>
+      <c r="I565" s="21" t="inlineStr">
+        <is>
+          <t>Switch + compute SSH</t>
+        </is>
+      </c>
+      <c r="J565" s="21" t="inlineStr">
+        <is>
+          <t>Health check (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K565" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (15 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L565" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" hidden="1" ht="112" customHeight="1" s="33">
+      <c r="A566" s="7" t="inlineStr">
+        <is>
           <t>HC-002</t>
         </is>
       </c>
-      <c r="B565" s="7" t="inlineStr">
+      <c r="B566" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C565" s="5" t="inlineStr">
+      <c r="C566" s="5" t="inlineStr">
         <is>
           <t>Health check: every tray's BMC reports chassis power on</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr">
+      <c r="G566" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H565" s="21" t="inlineStr">
+      <c r="H566" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-15 14:47 UTC (run g02-g17-20261015-151528), health result g02-g17-20261016-135436-merged] Skipped (not configured): Skipped: commands.health.bmc_power not set (e.g. 'IPMI_PASSWORD="$HELIOS_BMC_PASSWORD" ipmitool -I lanplus -H {bmc} -U &lt;user&gt; -E chassis power status')</t>
         </is>
       </c>
-      <c r="I565" s="21" t="inlineStr">
+      <c r="I566" s="21" t="inlineStr">
         <is>
           <t>BMC (ipmitool from the runner) + BMC credentials</t>
         </is>
       </c>
-      <c r="J565" s="21" t="inlineStr">
+      <c r="J566" s="21" t="inlineStr">
         <is>
           <t>Health check (Compute BMC)</t>
         </is>
       </c>
-      <c r="K565" s="21" t="inlineStr">
+      <c r="K566" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (15 Oct 2026)</t>
         </is>
       </c>
-      <c r="L565" s="21" t="inlineStr">
+      <c r="L566" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
-      <c r="M565" t="inlineStr">
+      <c r="M566" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
     </row>
-    <row r="566" hidden="1" ht="96" customHeight="1" s="33">
-      <c r="A566" s="7" t="inlineStr">
+    <row r="567" hidden="1" ht="96" customHeight="1" s="33">
+      <c r="A567" s="7" t="inlineStr">
         <is>
           <t>HC-003</t>
         </is>
       </c>
-      <c r="B566" s="7" t="inlineStr">
+      <c r="B567" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C566" s="5" t="inlineStr">
+      <c r="C567" s="5" t="inlineStr">
         <is>
           <t>Health check: afmctl lists every GPU of each tray and every device is ACTIVE</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F566" t="inlineStr">
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr">
+      <c r="G567" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H566" s="21" t="inlineStr">
+      <c r="H567" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
         </is>
       </c>
-      <c r="I566" s="21" t="inlineStr">
+      <c r="I567" s="21" t="inlineStr">
         <is>
           <t>Compute SSH (afmctl)</t>
         </is>
       </c>
-      <c r="J566" s="21" t="inlineStr">
+      <c r="J567" s="21" t="inlineStr">
         <is>
           <t>Health check (Compute)</t>
         </is>
       </c>
-      <c r="K566" s="21" t="inlineStr">
+      <c r="K567" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (15 Oct 2026)</t>
         </is>
       </c>
-      <c r="L566" s="21" t="inlineStr">
+      <c r="L567" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
-      <c r="M566" t="inlineStr">
+      <c r="M567" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
     </row>
-    <row r="567" hidden="1" ht="80" customHeight="1" s="33">
-      <c r="A567" s="7" t="inlineStr">
+    <row r="568" hidden="1" ht="80" customHeight="1" s="33">
+      <c r="A568" s="7" t="inlineStr">
         <is>
           <t>HC-004</t>
         </is>
       </c>
-      <c r="B567" s="7" t="inlineStr">
+      <c r="B568" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C567" s="5" t="inlineStr">
+      <c r="C568" s="5" t="inlineStr">
         <is>
           <t>Health check: no other workload using the GPUs (amd-smi process)</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
+      <c r="G568" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H567" s="21" t="inlineStr">
+      <c r="H568" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
         </is>
       </c>
-      <c r="I567" s="21" t="inlineStr">
+      <c r="I568" s="21" t="inlineStr">
         <is>
           <t>Compute SSH (amd-smi)</t>
         </is>
       </c>
-      <c r="J567" s="21" t="inlineStr">
+      <c r="J568" s="21" t="inlineStr">
         <is>
           <t>Health check (Compute)</t>
         </is>
       </c>
-      <c r="K567" s="21" t="inlineStr">
+      <c r="K568" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (15 Oct 2026)</t>
         </is>
       </c>
-      <c r="L567" s="21" t="inlineStr">
+      <c r="L568" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
-      <c r="M567" t="inlineStr">
+      <c r="M568" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
     </row>
-    <row r="568" hidden="1" ht="96" customHeight="1" s="33">
-      <c r="A568" s="7" t="inlineStr">
+    <row r="569" hidden="1" ht="96" customHeight="1" s="33">
+      <c r="A569" s="7" t="inlineStr">
         <is>
           <t>HC-005</t>
         </is>
       </c>
-      <c r="B568" s="7" t="inlineStr">
+      <c r="B569" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C568" s="5" t="inlineStr">
+      <c r="C569" s="5" t="inlineStr">
         <is>
           <t>Health check: no GPU ECC errors, no uncorrected machine checks and no AER / amdgpu / IFoE kernel errors on the trays (corrected machine checks counted)</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F568" t="inlineStr">
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr">
+      <c r="G569" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H568" s="21" t="inlineStr">
+      <c r="H569" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
         </is>
       </c>
-      <c r="I568" s="21" t="inlineStr">
+      <c r="I569" s="21" t="inlineStr">
         <is>
           <t>Compute SSH (amd-smi, journalctl)</t>
         </is>
       </c>
-      <c r="J568" s="21" t="inlineStr">
+      <c r="J569" s="21" t="inlineStr">
         <is>
           <t>Health check (Compute)</t>
         </is>
       </c>
-      <c r="K568" s="21" t="inlineStr">
+      <c r="K569" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (15 Oct 2026)</t>
         </is>
       </c>
-      <c r="L568" s="21" t="inlineStr">
+      <c r="L569" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
-      <c r="M568" t="inlineStr">
+      <c r="M569" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
     </row>
-    <row r="569" hidden="1" ht="80" customHeight="1" s="33">
-      <c r="A569" s="7" t="inlineStr">
+    <row r="570" hidden="1" ht="80" customHeight="1" s="33">
+      <c r="A570" s="7" t="inlineStr">
         <is>
           <t>HC-006</t>
         </is>
       </c>
-      <c r="B569" s="7" t="inlineStr">
+      <c r="B570" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C569" s="5" t="inlineStr">
+      <c r="C570" s="5" t="inlineStr">
         <is>
           <t>Health check: tray disk and memory headroom</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr">
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="G569" t="inlineStr">
+      <c r="G570" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H569" s="21" t="inlineStr">
+      <c r="H570" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
         </is>
       </c>
-      <c r="I569" s="21" t="inlineStr">
+      <c r="I570" s="21" t="inlineStr">
         <is>
           <t>Compute SSH</t>
         </is>
       </c>
-      <c r="J569" s="21" t="inlineStr">
+      <c r="J570" s="21" t="inlineStr">
         <is>
           <t>Health check (Compute)</t>
         </is>
       </c>
-      <c r="K569" s="21" t="inlineStr">
+      <c r="K570" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (15 Oct 2026)</t>
         </is>
       </c>
-      <c r="L569" s="21" t="inlineStr">
+      <c r="L570" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
-      <c r="M569" t="inlineStr">
+      <c r="M570" t="inlineStr">
         <is>
           <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="570" hidden="1" ht="96" customHeight="1" s="33">
-      <c r="A570" s="7" t="inlineStr">
-        <is>
-          <t>HC-007</t>
-        </is>
-      </c>
-      <c r="B570" s="7" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C570" s="5" t="inlineStr">
-        <is>
-          <t>Health check: no leftover helios-* test objects in AFM (vPODs, policies, users, roles, role bindings)</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F570" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
-        </is>
-      </c>
-      <c r="H570" s="21" t="inlineStr">
-        <is>
-          <t>[g02-g17 full rack, rack health check: ran 2026-10-15 14:43 UTC (run g02-g17-20261015-151528), health result g02-g17-20261016-135436-merged] PASS.</t>
-        </is>
-      </c>
-      <c r="I570" s="21" t="inlineStr">
-        <is>
-          <t>AFM API</t>
-        </is>
-      </c>
-      <c r="J570" s="21" t="inlineStr">
-        <is>
-          <t>Health check (Switch (AFM API))</t>
-        </is>
-      </c>
-      <c r="K570" s="21" t="inlineStr">
-        <is>
-          <t>Added - helios-tests (15 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="L570" s="21" t="inlineStr">
-        <is>
-          <t>Non-disruptive</t>
-        </is>
-      </c>
-      <c r="M570" t="inlineStr">
-        <is>
-          <t>Blocker</t>
         </is>
       </c>
     </row>
     <row r="571" hidden="1" ht="96" customHeight="1" s="33">
       <c r="A571" s="7" t="inlineStr">
         <is>
+          <t>HC-007</t>
+        </is>
+      </c>
+      <c r="B571" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>Health check: no leftover helios-* test objects in AFM (vPODs, policies, users, roles, role bindings)</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
+        </is>
+      </c>
+      <c r="H571" s="21" t="inlineStr">
+        <is>
+          <t>[g02-g17 full rack, rack health check: ran 2026-10-15 14:43 UTC (run g02-g17-20261015-151528), health result g02-g17-20261016-135436-merged] PASS.</t>
+        </is>
+      </c>
+      <c r="I571" s="21" t="inlineStr">
+        <is>
+          <t>AFM API</t>
+        </is>
+      </c>
+      <c r="J571" s="21" t="inlineStr">
+        <is>
+          <t>Health check (Switch (AFM API))</t>
+        </is>
+      </c>
+      <c r="K571" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (15 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L571" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Blocker</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" hidden="1" ht="96" customHeight="1" s="33">
+      <c r="A572" s="7" t="inlineStr">
+        <is>
           <t>HC-008</t>
         </is>
       </c>
-      <c r="B571" s="7" t="inlineStr">
+      <c r="B572" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C571" s="5" t="inlineStr">
+      <c r="C572" s="5" t="inlineStr">
         <is>
           <t>Health check: no critical AFM events in the recent window</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F571" t="inlineStr">
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G571" t="inlineStr">
+      <c r="G572" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H571" s="21" t="inlineStr">
+      <c r="H572" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 full rack, rack health check: ran 2026-10-15 14:43 UTC (run g02-g17-20261015-151528), health result g02-g17-20261016-135436-merged] PASS.</t>
         </is>
       </c>
-      <c r="I571" s="21" t="inlineStr">
+      <c r="I572" s="21" t="inlineStr">
         <is>
           <t>AFM API</t>
-        </is>
-      </c>
-      <c r="J571" s="21" t="inlineStr">
-        <is>
-          <t>Health check (Switch (AFM API))</t>
-        </is>
-      </c>
-      <c r="K571" s="21" t="inlineStr">
-        <is>
-          <t>Added - helios-tests (15 Oct 2026)</t>
-        </is>
-      </c>
-      <c r="L571" s="21" t="inlineStr">
-        <is>
-          <t>Non-disruptive</t>
-        </is>
-      </c>
-      <c r="M571" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="572" hidden="1" ht="32" customHeight="1" s="33">
-      <c r="A572" s="7" t="inlineStr">
-        <is>
-          <t>HC-009</t>
-        </is>
-      </c>
-      <c r="B572" s="7" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="C572" s="5" t="inlineStr">
-        <is>
-          <t>Health check: AFM controllers up for a while (no recent restart)</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F572" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
-        </is>
-      </c>
-      <c r="H572" s="21" t="inlineStr">
-        <is>
-          <t>[g02-g17 full rack, rack health check: ran 2026-10-15 14:43 UTC (run g02-g17-20261015-151528), health result g02-g17-20261016-135436-merged] PASS.</t>
-        </is>
-      </c>
-      <c r="I572" s="21" t="inlineStr">
-        <is>
-          <t>AFM API + switch SSH</t>
         </is>
       </c>
       <c r="J572" s="21" t="inlineStr">
@@ -36185,7 +36186,7 @@
     <row r="573" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A573" s="7" t="inlineStr">
         <is>
-          <t>HC-010</t>
+          <t>HC-009</t>
         </is>
       </c>
       <c r="B573" s="7" t="inlineStr">
@@ -36195,7 +36196,7 @@
       </c>
       <c r="C573" s="5" t="inlineStr">
         <is>
-          <t>Health check: same amdgpu, ROCm, IFoE, afmctl and GPU firmware versions on every tray</t>
+          <t>Health check: AFM controllers up for a while (no recent restart)</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -36205,7 +36206,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -36215,17 +36216,17 @@
       </c>
       <c r="H573" s="21" t="inlineStr">
         <is>
-          <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
+          <t>[g02-g17 full rack, rack health check: ran 2026-10-15 14:43 UTC (run g02-g17-20261015-151528), health result g02-g17-20261016-135436-merged] PASS.</t>
         </is>
       </c>
       <c r="I573" s="21" t="inlineStr">
         <is>
-          <t>Compute SSH (amd-smi)</t>
+          <t>AFM API + switch SSH</t>
         </is>
       </c>
       <c r="J573" s="21" t="inlineStr">
         <is>
-          <t>Health check (Compute)</t>
+          <t>Health check (Switch (AFM API))</t>
         </is>
       </c>
       <c r="K573" s="21" t="inlineStr">
@@ -36247,7 +36248,7 @@
     <row r="574" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A574" s="7" t="inlineStr">
         <is>
-          <t>HC-011</t>
+          <t>HC-010</t>
         </is>
       </c>
       <c r="B574" s="7" t="inlineStr">
@@ -36257,7 +36258,7 @@
       </c>
       <c r="C574" s="5" t="inlineStr">
         <is>
-          <t>Health check: hardware inventory and usage of every switch and tray (CPU, memory, disks, GPUs, compute&lt;-&gt;switch links up / down)</t>
+          <t>Health check: same amdgpu, ROCm, IFoE, afmctl and GPU firmware versions on every tray</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -36282,12 +36283,12 @@
       </c>
       <c r="I574" s="21" t="inlineStr">
         <is>
-          <t>Switch + compute SSH (amd-smi, afmctl)</t>
+          <t>Compute SSH (amd-smi)</t>
         </is>
       </c>
       <c r="J574" s="21" t="inlineStr">
         <is>
-          <t>Health check (Switch + Compute)</t>
+          <t>Health check (Compute)</t>
         </is>
       </c>
       <c r="K574" s="21" t="inlineStr">
@@ -36309,117 +36310,132 @@
     <row r="575" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A575" s="7" t="inlineStr">
         <is>
+          <t>HC-011</t>
+        </is>
+      </c>
+      <c r="B575" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C575" s="5" t="inlineStr">
+        <is>
+          <t>Health check: hardware inventory and usage of every switch and tray (CPU, memory, disks, GPUs, compute&lt;-&gt;switch links up / down)</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
+        </is>
+      </c>
+      <c r="H575" s="21" t="inlineStr">
+        <is>
+          <t>[g02-g17 full rack, rack health check: ran 2026-10-16 05:27 UTC (run g02-g17-20261016-053848), health result g02-g17-20261016-135436-merged] PARTIAL: fails only because CT05 (10.255.4.51) is unreachable - the health check groups it under the root cause "ct05 unreachable"; passed on every reachable node.</t>
+        </is>
+      </c>
+      <c r="I575" s="21" t="inlineStr">
+        <is>
+          <t>Switch + compute SSH (amd-smi, afmctl)</t>
+        </is>
+      </c>
+      <c r="J575" s="21" t="inlineStr">
+        <is>
+          <t>Health check (Switch + Compute)</t>
+        </is>
+      </c>
+      <c r="K575" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (15 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L575" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" hidden="1" ht="32" customHeight="1" s="33">
+      <c r="A576" s="7" t="inlineStr">
+        <is>
           <t>HC-012</t>
         </is>
       </c>
-      <c r="B575" s="7" t="inlineStr">
+      <c r="B576" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C575" s="5" t="inlineStr">
+      <c r="C576" s="5" t="inlineStr">
         <is>
           <t>Health check: link scan - every GPU link of the rack checked end to end with one root cause per down / degraded link (helios-debug link_check, run as a separate tool)</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F575" t="inlineStr">
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="G575" t="inlineStr">
+      <c r="G576" t="inlineStr">
         <is>
           <t>SONiC.202505I20260915070938_x100.15; afm-agent/controller 202505I20260915070938_x100.15; ROCm 10.2.0a20260922</t>
         </is>
       </c>
-      <c r="H575" s="21" t="inlineStr">
+      <c r="H576" s="21" t="inlineStr">
         <is>
           <t>[g02-g17 health check HC-012, 19 Oct 2026 01:22 UTC, run g02-g17-20261019-012258, link report results/runs/g02-g17/link-scans/scan-20261019-012215] FAIL: 2,592 links, 2,443 ok, 149 down - 144 of them CT05 (quarantined, recorded not failed); 5 real: 4 with no physical link on either end after being up (st4 Ethernet66 = CT18 port 28, st4 Ethernet70 = CT17 port 24, st6 Ethernet261 = CT13 port 0, st6 Ethernet257 = CT14 port 2; switch ASIC: lane 0 dark on three, no signal on either lane on Ethernet261) and 1 never up since boot (st5 Ethernet494 = CT16 port 5, clean signal that never locks). All on GPU position 0002:01:00.1 - on-site check.
 [MR2 mini rack, HC-012, 19 Oct 2026 01:21 UTC, run mr2-20261018-182146 (helios-tests-ui), link report results/runs/mr2/link-scans/scan-20261019-012107] PASS: 288 GPU links (1 switch st1, 2 ASICs; 2 trays x 4 GPUs x 36 ports), 288 ok; st1 asic0 carries GPU ports 18-35 and asic1 ports 0-17 of both trays; matched by GPU port MAC; IFCP not running on MR2 (judged on the other layers; L2 ping between the trays passes on every port tested). First attempt 01:18 UTC (run mr2-20261018-181857) FAIL: st1 had no static forwarding entries for ~30 s (AFM reprogramming), so no port could be matched - the scan now re-reads an empty table and names that cause.</t>
         </is>
       </c>
-      <c r="I575" s="21" t="inlineStr">
+      <c r="I576" s="21" t="inlineStr">
         <is>
           <t>Switch SSH + compute SSH (helios-debug link_check)</t>
         </is>
       </c>
-      <c r="J575" s="21" t="inlineStr">
+      <c r="J576" s="21" t="inlineStr">
         <is>
           <t>Health check (Switch + Compute)</t>
         </is>
       </c>
-      <c r="K575" s="21" t="inlineStr">
+      <c r="K576" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (19 Oct 2026)</t>
         </is>
       </c>
-      <c r="L575" s="21" t="inlineStr">
+      <c r="L576" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
-      <c r="M575" t="inlineStr">
+      <c r="M576" t="inlineStr">
         <is>
           <t>Warning</t>
-        </is>
-      </c>
-    </row>
-    <row r="576" hidden="1" ht="32" customHeight="1" s="33">
-      <c r="A576" s="7" t="inlineStr">
-        <is>
-          <t>TC-AFM-058</t>
-        </is>
-      </c>
-      <c r="B576" s="7" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="C576" s="5" t="inlineStr">
-        <is>
-          <t>Validate that the IFoE station path-to-port mapping (afmctl show station) is cor</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H576" s="21" t="inlineStr">
-        <is>
-          <t>Not run on g02-g17 yet: automated (afmctl show station mapping vs AFM), not in the executed batches. Listed on the "afm" sheet of the plan.</t>
-        </is>
-      </c>
-      <c r="I576" s="21" t="inlineStr">
-        <is>
-          <t>AFM API + compute SSH</t>
-        </is>
-      </c>
-      <c r="J576" s="21" t="inlineStr">
-        <is>
-          <t>Switch (AFM API)</t>
-        </is>
-      </c>
-      <c r="K576" s="21" t="inlineStr">
-        <is>
-          <t>BKC-26.12 plan</t>
-        </is>
-      </c>
-      <c r="L576" s="21" t="inlineStr">
-        <is>
-          <t>Non-disruptive</t>
         </is>
       </c>
     </row>
     <row r="577" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A577" s="7" t="inlineStr">
         <is>
-          <t>TC-AFM-060</t>
+          <t>TC-AFM-058</t>
         </is>
       </c>
       <c r="B577" s="7" t="inlineStr">
@@ -36429,7 +36445,7 @@
       </c>
       <c r="C577" s="5" t="inlineStr">
         <is>
-          <t>Validate that the IFoE station port-to-path mapping (afmctl show station) and th</t>
+          <t>Validate that the IFoE station path-to-port mapping (afmctl show station) is cor</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -36466,17 +36482,17 @@
     <row r="578" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A578" s="7" t="inlineStr">
         <is>
-          <t>TC-IBS-001</t>
+          <t>TC-AFM-060</t>
         </is>
       </c>
       <c r="B578" s="7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C578" s="5" t="inlineStr">
         <is>
-          <t>Basic crossnode bandwidth test</t>
+          <t>Validate that the IFoE station port-to-path mapping (afmctl show station) and th</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -36486,17 +36502,17 @@
       </c>
       <c r="H578" s="21" t="inlineStr">
         <is>
-          <t>Not run on g02-g17: automated (scale-out RDMA bandwidth over the compute trays' scale-out NICs, tests/scaleout); not scheduled - g02-g17 testing covers the scale-up fabric. Listed on the "mortaro" sheet of the plan.</t>
+          <t>Not run on g02-g17 yet: automated (afmctl show station mapping vs AFM), not in the executed batches. Listed on the "afm" sheet of the plan.</t>
         </is>
       </c>
       <c r="I578" s="21" t="inlineStr">
         <is>
-          <t>Compute SSH + scale-out NICs</t>
+          <t>AFM API + compute SSH</t>
         </is>
       </c>
       <c r="J578" s="21" t="inlineStr">
         <is>
-          <t>Compute</t>
+          <t>Switch (AFM API)</t>
         </is>
       </c>
       <c r="K578" s="21" t="inlineStr">
@@ -36513,7 +36529,7 @@
     <row r="579" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A579" s="7" t="inlineStr">
         <is>
-          <t>TC-IBS-002</t>
+          <t>TC-IBS-001</t>
         </is>
       </c>
       <c r="B579" s="7" t="inlineStr">
@@ -36523,7 +36539,7 @@
       </c>
       <c r="C579" s="5" t="inlineStr">
         <is>
-          <t>Multi-verb bandwidth sweep</t>
+          <t>Basic crossnode bandwidth test</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -36560,17 +36576,17 @@
     <row r="580" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A580" s="7" t="inlineStr">
         <is>
-          <t>TC-IBS-003</t>
+          <t>TC-IBS-002</t>
         </is>
       </c>
       <c r="B580" s="7" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C580" s="5" t="inlineStr">
         <is>
-          <t>Queue pair scaling test</t>
+          <t>Multi-verb bandwidth sweep</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -36607,17 +36623,17 @@
     <row r="581" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A581" s="7" t="inlineStr">
         <is>
-          <t>TC-IBS-004</t>
+          <t>TC-IBS-003</t>
         </is>
       </c>
       <c r="B581" s="7" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C581" s="5" t="inlineStr">
         <is>
-          <t>Full parameter matrix regression</t>
+          <t>Queue pair scaling test</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -36654,17 +36670,17 @@
     <row r="582" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A582" s="7" t="inlineStr">
         <is>
-          <t>TC-IBS-005</t>
+          <t>TC-IBS-004</t>
         </is>
       </c>
       <c r="B582" s="7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="C582" s="5" t="inlineStr">
         <is>
-          <t>Single-node loopback bandwidth test</t>
+          <t>Full parameter matrix regression</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -36701,17 +36717,17 @@
     <row r="583" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A583" s="7" t="inlineStr">
         <is>
-          <t>TC-IBS-006</t>
+          <t>TC-IBS-005</t>
         </is>
       </c>
       <c r="B583" s="7" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C583" s="5" t="inlineStr">
         <is>
-          <t>Fully configurable test case</t>
+          <t>Single-node loopback bandwidth test</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -36748,17 +36764,17 @@
     <row r="584" ht="32" customHeight="1" s="33">
       <c r="A584" s="7" t="inlineStr">
         <is>
-          <t>TC-BMC-001</t>
+          <t>TC-IBS-006</t>
         </is>
       </c>
       <c r="B584" s="7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="C584" s="5" t="inlineStr">
         <is>
-          <t>BMC reachable and login works: every switch and compute BMC answers Redfish at its own address (bmc:) with its bmc_user and BMC password</t>
+          <t>Fully configurable test case</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -36766,29 +36782,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="H584" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
+          <t>Not run on g02-g17: automated (scale-out RDMA bandwidth over the compute trays' scale-out NICs, tests/scaleout); not scheduled - g02-g17 testing covers the scale-up fabric. Listed on the "mortaro" sheet of the plan.</t>
         </is>
       </c>
       <c r="I584" s="21" t="inlineStr">
         <is>
-          <t>BMC Redfish (HTTPS) from the test runner</t>
+          <t>Compute SSH + scale-out NICs</t>
         </is>
       </c>
       <c r="J584" s="21" t="inlineStr">
         <is>
-          <t>BMC (Switch + Compute)</t>
+          <t>Compute</t>
         </is>
       </c>
       <c r="K584" s="21" t="inlineStr">
         <is>
-          <t>Added - helios-tests (20 Oct 2026)</t>
+          <t>BKC-26.12 plan</t>
         </is>
       </c>
       <c r="L584" s="21" t="inlineStr">
@@ -36800,7 +36811,7 @@
     <row r="585" ht="32" customHeight="1" s="33">
       <c r="A585" s="7" t="inlineStr">
         <is>
-          <t>TC-BMC-002</t>
+          <t>TC-BMC-001</t>
         </is>
       </c>
       <c r="B585" s="7" t="inlineStr">
@@ -36810,7 +36821,7 @@
       </c>
       <c r="C585" s="5" t="inlineStr">
         <is>
-          <t>BMC power state: every system the switch and compute BMCs report is powered on</t>
+          <t>BMC reachable and login works: every switch and compute BMC answers Redfish at its own address (bmc:) with its bmc_user and BMC password</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -36852,7 +36863,7 @@
     <row r="586" ht="32" customHeight="1" s="33">
       <c r="A586" s="7" t="inlineStr">
         <is>
-          <t>TC-BMC-003</t>
+          <t>TC-BMC-002</t>
         </is>
       </c>
       <c r="B586" s="7" t="inlineStr">
@@ -36862,7 +36873,7 @@
       </c>
       <c r="C586" s="5" t="inlineStr">
         <is>
-          <t>BMC health: no BMC (manager) or system reports health Critical (Warning recorded)</t>
+          <t>BMC power state: every system the switch and compute BMCs report is powered on</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -36904,7 +36915,7 @@
     <row r="587" ht="32" customHeight="1" s="33">
       <c r="A587" s="7" t="inlineStr">
         <is>
-          <t>TC-BMC-004</t>
+          <t>TC-BMC-003</t>
         </is>
       </c>
       <c r="B587" s="7" t="inlineStr">
@@ -36914,7 +36925,7 @@
       </c>
       <c r="C587" s="5" t="inlineStr">
         <is>
-          <t>BMC sensors: no temperature, fan, voltage or power-supply sensor Critical or beyond its critical limit (beyond a non-critical limit recorded)</t>
+          <t>BMC health: no BMC (manager) or system reports health Critical (Warning recorded)</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -36956,7 +36967,7 @@
     <row r="588" ht="32" customHeight="1" s="33">
       <c r="A588" s="7" t="inlineStr">
         <is>
-          <t>TC-BMC-005</t>
+          <t>TC-BMC-004</t>
         </is>
       </c>
       <c r="B588" s="7" t="inlineStr">
@@ -36966,7 +36977,7 @@
       </c>
       <c r="C588" s="5" t="inlineStr">
         <is>
-          <t>BMC event log: no Critical entry in the last 24 h (thresholds.bmc.log_window_h); Warning entries counted</t>
+          <t>BMC sensors: no temperature, fan, voltage or power-supply sensor Critical or beyond its critical limit (beyond a non-critical limit recorded)</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -37008,17 +37019,17 @@
     <row r="589" ht="32" customHeight="1" s="33">
       <c r="A589" s="7" t="inlineStr">
         <is>
-          <t>TC-BMC-006</t>
+          <t>TC-BMC-005</t>
         </is>
       </c>
       <c r="B589" s="7" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="C589" s="5" t="inlineStr">
         <is>
-          <t>BMC firmware consistent: same BMC firmware version on every compute tray, and on every switch tray</t>
+          <t>BMC event log: no Critical entry in the last 24 h (thresholds.bmc.log_window_h); Warning entries counted</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -37060,17 +37071,17 @@
     <row r="590" ht="32" customHeight="1" s="33">
       <c r="A590" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.1-1</t>
+          <t>TC-BMC-006</t>
         </is>
       </c>
       <c r="B590" s="7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="C590" s="5" t="inlineStr">
         <is>
-          <t>GET Service Root (Tc7.2.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>BMC firmware consistent: same BMC firmware version on every compute tray, and on every switch tray</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -37085,17 +37096,17 @@
       </c>
       <c r="H590" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026, automated (tests/bmc/test_bmc.py, read-only Redfish); needs each node's bmc / bmc_user in the inventory and a BMC password (UI: Inventory tab default or Setup node table)</t>
         </is>
       </c>
       <c r="I590" s="21" t="inlineStr">
         <is>
-          <t>Switch BMC Redfish (HTTPS)</t>
+          <t>BMC Redfish (HTTPS) from the test runner</t>
         </is>
       </c>
       <c r="J590" s="21" t="inlineStr">
         <is>
-          <t>BMC (Switch)</t>
+          <t>BMC (Switch + Compute)</t>
         </is>
       </c>
       <c r="K590" s="21" t="inlineStr">
@@ -37112,7 +37123,7 @@
     <row r="591" ht="32" customHeight="1" s="33">
       <c r="A591" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.1-2</t>
+          <t>TC-BLT-7.2.1-1</t>
         </is>
       </c>
       <c r="B591" s="7" t="inlineStr">
@@ -37122,7 +37133,7 @@
       </c>
       <c r="C591" s="5" t="inlineStr">
         <is>
-          <t>GET OData Service Document (Tc7.2.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Service Root (Tc7.2.1-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -37137,7 +37148,7 @@
       </c>
       <c r="H591" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I591" s="21" t="inlineStr">
@@ -37164,7 +37175,7 @@
     <row r="592" ht="32" customHeight="1" s="33">
       <c r="A592" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.1-3</t>
+          <t>TC-BLT-7.2.1-2</t>
         </is>
       </c>
       <c r="B592" s="7" t="inlineStr">
@@ -37174,7 +37185,7 @@
       </c>
       <c r="C592" s="5" t="inlineStr">
         <is>
-          <t>GET Schema Metadata ($metadata) (Tc7.2.1-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET OData Service Document (Tc7.2.1-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -37189,7 +37200,7 @@
       </c>
       <c r="H592" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I592" s="21" t="inlineStr">
@@ -37216,7 +37227,7 @@
     <row r="593" ht="32" customHeight="1" s="33">
       <c r="A593" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.2-1</t>
+          <t>TC-BLT-7.2.1-3</t>
         </is>
       </c>
       <c r="B593" s="7" t="inlineStr">
@@ -37226,7 +37237,7 @@
       </c>
       <c r="C593" s="5" t="inlineStr">
         <is>
-          <t>List Chassis Collection (Tc7.2.2-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Schema Metadata ($metadata) (Tc7.2.1-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -37241,7 +37252,7 @@
       </c>
       <c r="H593" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.1-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I593" s="21" t="inlineStr">
@@ -37268,7 +37279,7 @@
     <row r="594" ht="32" customHeight="1" s="33">
       <c r="A594" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.2-2</t>
+          <t>TC-BLT-7.2.2-1</t>
         </is>
       </c>
       <c r="B594" s="7" t="inlineStr">
@@ -37278,7 +37289,7 @@
       </c>
       <c r="C594" s="5" t="inlineStr">
         <is>
-          <t>Get Chassis Detail (Tc7.2.2-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Chassis Collection (Tc7.2.2-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -37293,7 +37304,7 @@
       </c>
       <c r="H594" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I594" s="21" t="inlineStr">
@@ -37320,7 +37331,7 @@
     <row r="595" ht="32" customHeight="1" s="33">
       <c r="A595" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.2-3</t>
+          <t>TC-BLT-7.2.2-2</t>
         </is>
       </c>
       <c r="B595" s="7" t="inlineStr">
@@ -37330,7 +37341,7 @@
       </c>
       <c r="C595" s="5" t="inlineStr">
         <is>
-          <t>Get System Detail (Tc7.2.2-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Get Chassis Detail (Tc7.2.2-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -37345,7 +37356,7 @@
       </c>
       <c r="H595" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I595" s="21" t="inlineStr">
@@ -37372,7 +37383,7 @@
     <row r="596" ht="32" customHeight="1" s="33">
       <c r="A596" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.3-1</t>
+          <t>TC-BLT-7.2.2-3</t>
         </is>
       </c>
       <c r="B596" s="7" t="inlineStr">
@@ -37382,7 +37393,7 @@
       </c>
       <c r="C596" s="5" t="inlineStr">
         <is>
-          <t>List All Sensors (Tc7.2.3-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Get System Detail (Tc7.2.2-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -37397,7 +37408,7 @@
       </c>
       <c r="H596" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.2-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I596" s="21" t="inlineStr">
@@ -37424,7 +37435,7 @@
     <row r="597" ht="32" customHeight="1" s="33">
       <c r="A597" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.3-2</t>
+          <t>TC-BLT-7.2.3-1</t>
         </is>
       </c>
       <c r="B597" s="7" t="inlineStr">
@@ -37434,7 +37445,7 @@
       </c>
       <c r="C597" s="5" t="inlineStr">
         <is>
-          <t>Get Individual Sensor (LeakDetector_0) (Tc7.2.3-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List All Sensors (Tc7.2.3-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -37449,7 +37460,7 @@
       </c>
       <c r="H597" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I597" s="21" t="inlineStr">
@@ -37476,7 +37487,7 @@
     <row r="598" ht="32" customHeight="1" s="33">
       <c r="A598" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.3-3</t>
+          <t>TC-BLT-7.2.3-2</t>
         </is>
       </c>
       <c r="B598" s="7" t="inlineStr">
@@ -37486,7 +37497,7 @@
       </c>
       <c r="C598" s="5" t="inlineStr">
         <is>
-          <t>Legacy Thermal View (Tc7.2.3-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Get Individual Sensor (LeakDetector_0) (Tc7.2.3-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -37501,7 +37512,7 @@
       </c>
       <c r="H598" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I598" s="21" t="inlineStr">
@@ -37528,7 +37539,7 @@
     <row r="599" ht="32" customHeight="1" s="33">
       <c r="A599" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.4-1</t>
+          <t>TC-BLT-7.2.3-3</t>
         </is>
       </c>
       <c r="B599" s="7" t="inlineStr">
@@ -37538,7 +37549,7 @@
       </c>
       <c r="C599" s="5" t="inlineStr">
         <is>
-          <t>LeakDetection Resource (Tc7.2.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Legacy Thermal View (Tc7.2.3-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -37553,7 +37564,7 @@
       </c>
       <c r="H599" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.3-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I599" s="21" t="inlineStr">
@@ -37580,7 +37591,7 @@
     <row r="600" ht="32" customHeight="1" s="33">
       <c r="A600" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.4-2</t>
+          <t>TC-BLT-7.2.4-1</t>
         </is>
       </c>
       <c r="B600" s="7" t="inlineStr">
@@ -37590,7 +37601,7 @@
       </c>
       <c r="C600" s="5" t="inlineStr">
         <is>
-          <t>List LeakDetectors (Tc7.2.4-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>LeakDetection Resource (Tc7.2.4-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -37605,7 +37616,7 @@
       </c>
       <c r="H600" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I600" s="21" t="inlineStr">
@@ -37632,7 +37643,7 @@
     <row r="601" ht="32" customHeight="1" s="33">
       <c r="A601" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.4-3</t>
+          <t>TC-BLT-7.2.4-2</t>
         </is>
       </c>
       <c r="B601" s="7" t="inlineStr">
@@ -37642,7 +37653,7 @@
       </c>
       <c r="C601" s="5" t="inlineStr">
         <is>
-          <t>LeakDetector Detail (Tc7.2.4-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List LeakDetectors (Tc7.2.4-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -37657,7 +37668,7 @@
       </c>
       <c r="H601" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I601" s="21" t="inlineStr">
@@ -37684,7 +37695,7 @@
     <row r="602" ht="32" customHeight="1" s="33">
       <c r="A602" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.5-1</t>
+          <t>TC-BLT-7.2.4-3</t>
         </is>
       </c>
       <c r="B602" s="7" t="inlineStr">
@@ -37694,7 +37705,7 @@
       </c>
       <c r="C602" s="5" t="inlineStr">
         <is>
-          <t>ThermalSubsystem Overview (Tc7.2.5-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>LeakDetector Detail (Tc7.2.4-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -37709,7 +37720,7 @@
       </c>
       <c r="H602" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.5-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.4-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I602" s="21" t="inlineStr">
@@ -37736,7 +37747,7 @@
     <row r="603" ht="32" customHeight="1" s="33">
       <c r="A603" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.6-1</t>
+          <t>TC-BLT-7.2.5-1</t>
         </is>
       </c>
       <c r="B603" s="7" t="inlineStr">
@@ -37746,7 +37757,7 @@
       </c>
       <c r="C603" s="5" t="inlineStr">
         <is>
-          <t>BMC Detail (Tc7.2.6-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>ThermalSubsystem Overview (Tc7.2.5-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -37761,7 +37772,7 @@
       </c>
       <c r="H603" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.5-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I603" s="21" t="inlineStr">
@@ -37788,7 +37799,7 @@
     <row r="604" ht="32" customHeight="1" s="33">
       <c r="A604" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.6-2</t>
+          <t>TC-BLT-7.2.6-1</t>
         </is>
       </c>
       <c r="B604" s="7" t="inlineStr">
@@ -37798,7 +37809,7 @@
       </c>
       <c r="C604" s="5" t="inlineStr">
         <is>
-          <t>NetworkProtocol (Tc7.2.6-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>BMC Detail (Tc7.2.6-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -37813,7 +37824,7 @@
       </c>
       <c r="H604" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I604" s="21" t="inlineStr">
@@ -37840,7 +37851,7 @@
     <row r="605" ht="32" customHeight="1" s="33">
       <c r="A605" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.7-1</t>
+          <t>TC-BLT-7.2.6-2</t>
         </is>
       </c>
       <c r="B605" s="7" t="inlineStr">
@@ -37850,7 +37861,7 @@
       </c>
       <c r="C605" s="5" t="inlineStr">
         <is>
-          <t>List Users (Tc7.2.7-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>NetworkProtocol (Tc7.2.6-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -37865,7 +37876,7 @@
       </c>
       <c r="H605" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.7-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I605" s="21" t="inlineStr">
@@ -37892,7 +37903,7 @@
     <row r="606" ht="32" customHeight="1" s="33">
       <c r="A606" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.7-7</t>
+          <t>TC-BLT-7.2.7-1</t>
         </is>
       </c>
       <c r="B606" s="7" t="inlineStr">
@@ -37902,7 +37913,7 @@
       </c>
       <c r="C606" s="5" t="inlineStr">
         <is>
-          <t>List Roles (Tc7.2.7-7, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Users (Tc7.2.7-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -37917,7 +37928,7 @@
       </c>
       <c r="H606" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.7-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.7-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I606" s="21" t="inlineStr">
@@ -37944,7 +37955,7 @@
     <row r="607" ht="32" customHeight="1" s="33">
       <c r="A607" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.8-3</t>
+          <t>TC-BLT-7.2.7-7</t>
         </is>
       </c>
       <c r="B607" s="7" t="inlineStr">
@@ -37954,7 +37965,7 @@
       </c>
       <c r="C607" s="5" t="inlineStr">
         <is>
-          <t>List Sessions (Tc7.2.8-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Roles (Tc7.2.7-7, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -37969,7 +37980,7 @@
       </c>
       <c r="H607" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.8-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.7-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I607" s="21" t="inlineStr">
@@ -37996,7 +38007,7 @@
     <row r="608" ht="32" customHeight="1" s="33">
       <c r="A608" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.9-1</t>
+          <t>TC-BLT-7.2.8-3</t>
         </is>
       </c>
       <c r="B608" s="7" t="inlineStr">
@@ -38006,7 +38017,7 @@
       </c>
       <c r="C608" s="5" t="inlineStr">
         <is>
-          <t>EventService Status (Tc7.2.9-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Sessions (Tc7.2.8-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -38021,7 +38032,7 @@
       </c>
       <c r="H608" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.8-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I608" s="21" t="inlineStr">
@@ -38048,7 +38059,7 @@
     <row r="609" ht="32" customHeight="1" s="33">
       <c r="A609" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.9-14</t>
+          <t>TC-BLT-7.2.9-1</t>
         </is>
       </c>
       <c r="B609" s="7" t="inlineStr">
@@ -38058,7 +38069,7 @@
       </c>
       <c r="C609" s="5" t="inlineStr">
         <is>
-          <t>Verify Chassis and Sensor URIs (Native Local - No Rewriting) (Tc7.2.9-14, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>EventService Status (Tc7.2.9-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -38073,7 +38084,7 @@
       </c>
       <c r="H609" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I609" s="21" t="inlineStr">
@@ -38100,7 +38111,7 @@
     <row r="610" ht="32" customHeight="1" s="33">
       <c r="A610" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.9-18</t>
+          <t>TC-BLT-7.2.9-14</t>
         </is>
       </c>
       <c r="B610" s="7" t="inlineStr">
@@ -38110,7 +38121,7 @@
       </c>
       <c r="C610" s="5" t="inlineStr">
         <is>
-          <t>Check Switch Manager / BMC Info (Tc7.2.9-18, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Chassis and Sensor URIs (Native Local - No Rewriting) (Tc7.2.9-14, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -38125,7 +38136,7 @@
       </c>
       <c r="H610" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-18); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I610" s="21" t="inlineStr">
@@ -38152,7 +38163,7 @@
     <row r="611" ht="32" customHeight="1" s="33">
       <c r="A611" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.10-1</t>
+          <t>TC-BLT-7.2.9-18</t>
         </is>
       </c>
       <c r="B611" s="7" t="inlineStr">
@@ -38162,7 +38173,7 @@
       </c>
       <c r="C611" s="5" t="inlineStr">
         <is>
-          <t>LogService Accessible on Switch BMC (Tc7.2.10-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Check Switch Manager / BMC Info (Tc7.2.9-18, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -38177,7 +38188,7 @@
       </c>
       <c r="H611" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.9-18); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I611" s="21" t="inlineStr">
@@ -38204,7 +38215,7 @@
     <row r="612" ht="32" customHeight="1" s="33">
       <c r="A612" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.10-13</t>
+          <t>TC-BLT-7.2.10-1</t>
         </is>
       </c>
       <c r="B612" s="7" t="inlineStr">
@@ -38214,7 +38225,7 @@
       </c>
       <c r="C612" s="5" t="inlineStr">
         <is>
-          <t>MaxNumberOfRecords = 10,000 (Tc7.2.10-13, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>LogService Accessible on Switch BMC (Tc7.2.10-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -38229,7 +38240,7 @@
       </c>
       <c r="H612" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I612" s="21" t="inlineStr">
@@ -38256,7 +38267,7 @@
     <row r="613" ht="32" customHeight="1" s="33">
       <c r="A613" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.10-14</t>
+          <t>TC-BLT-7.2.10-13</t>
         </is>
       </c>
       <c r="B613" s="7" t="inlineStr">
@@ -38266,7 +38277,7 @@
       </c>
       <c r="C613" s="5" t="inlineStr">
         <is>
-          <t>OverWritePolicy = "WrapsWhenFull" (Tc7.2.10-14, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>MaxNumberOfRecords = 10,000 (Tc7.2.10-13, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -38281,7 +38292,7 @@
       </c>
       <c r="H613" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I613" s="21" t="inlineStr">
@@ -38308,7 +38319,7 @@
     <row r="614" ht="32" customHeight="1" s="33">
       <c r="A614" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.10-15</t>
+          <t>TC-BLT-7.2.10-14</t>
         </is>
       </c>
       <c r="B614" s="7" t="inlineStr">
@@ -38318,7 +38329,7 @@
       </c>
       <c r="C614" s="5" t="inlineStr">
         <is>
-          <t>ClearLog Action Supported (Tc7.2.10-15, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>OverWritePolicy = "WrapsWhenFull" (Tc7.2.10-14, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -38333,7 +38344,7 @@
       </c>
       <c r="H614" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-15); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I614" s="21" t="inlineStr">
@@ -38360,7 +38371,7 @@
     <row r="615" ht="32" customHeight="1" s="33">
       <c r="A615" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.10-18</t>
+          <t>TC-BLT-7.2.10-15</t>
         </is>
       </c>
       <c r="B615" s="7" t="inlineStr">
@@ -38370,7 +38381,7 @@
       </c>
       <c r="C615" s="5" t="inlineStr">
         <is>
-          <t>All Three Table 37 Parameters Present Together (Tc7.2.10-18, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>ClearLog Action Supported (Tc7.2.10-15, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -38385,7 +38396,7 @@
       </c>
       <c r="H615" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-18); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-15); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I615" s="21" t="inlineStr">
@@ -38412,7 +38423,7 @@
     <row r="616" ht="32" customHeight="1" s="33">
       <c r="A616" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.11-1</t>
+          <t>TC-BLT-7.2.10-18</t>
         </is>
       </c>
       <c r="B616" s="7" t="inlineStr">
@@ -38422,7 +38433,7 @@
       </c>
       <c r="C616" s="5" t="inlineStr">
         <is>
-          <t>UpdateService Overview (Tc7.2.11-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>All Three Table 37 Parameters Present Together (Tc7.2.10-18, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -38437,7 +38448,7 @@
       </c>
       <c r="H616" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.11-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.10-18); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I616" s="21" t="inlineStr">
@@ -38464,7 +38475,7 @@
     <row r="617" ht="32" customHeight="1" s="33">
       <c r="A617" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.11-2</t>
+          <t>TC-BLT-7.2.11-1</t>
         </is>
       </c>
       <c r="B617" s="7" t="inlineStr">
@@ -38474,7 +38485,7 @@
       </c>
       <c r="C617" s="5" t="inlineStr">
         <is>
-          <t>Firmware Inventory (Tc7.2.11-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>UpdateService Overview (Tc7.2.11-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -38489,7 +38500,7 @@
       </c>
       <c r="H617" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.11-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.11-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I617" s="21" t="inlineStr">
@@ -38516,7 +38527,7 @@
     <row r="618" ht="32" customHeight="1" s="33">
       <c r="A618" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.4-1</t>
+          <t>TC-BLT-7.2.11-2</t>
         </is>
       </c>
       <c r="B618" s="7" t="inlineStr">
@@ -38526,7 +38537,7 @@
       </c>
       <c r="C618" s="5" t="inlineStr">
         <is>
-          <t>GET UpdateService - Configuration (Tc7.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Firmware Inventory (Tc7.2.11-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -38541,7 +38552,7 @@
       </c>
       <c r="H618" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.11-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I618" s="21" t="inlineStr">
@@ -38568,7 +38579,7 @@
     <row r="619" ht="32" customHeight="1" s="33">
       <c r="A619" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.4-2</t>
+          <t>TC-BLT-7.4-1</t>
         </is>
       </c>
       <c r="B619" s="7" t="inlineStr">
@@ -38578,7 +38589,7 @@
       </c>
       <c r="C619" s="5" t="inlineStr">
         <is>
-          <t>GET FirmwareInventory - Switch Collection (Tc7.4-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET UpdateService - Configuration (Tc7.4-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -38593,7 +38604,7 @@
       </c>
       <c r="H619" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I619" s="21" t="inlineStr">
@@ -38620,7 +38631,7 @@
     <row r="620" ht="32" customHeight="1" s="33">
       <c r="A620" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.4-6</t>
+          <t>TC-BLT-7.4-2</t>
         </is>
       </c>
       <c r="B620" s="7" t="inlineStr">
@@ -38630,7 +38641,7 @@
       </c>
       <c r="C620" s="5" t="inlineStr">
         <is>
-          <t>GET FirmwareInventory/{id} - Individual Entry (Tc7.4-6, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET FirmwareInventory - Switch Collection (Tc7.4-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -38645,7 +38656,7 @@
       </c>
       <c r="H620" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I620" s="21" t="inlineStr">
@@ -38672,7 +38683,7 @@
     <row r="621" ht="32" customHeight="1" s="33">
       <c r="A621" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.4-7</t>
+          <t>TC-BLT-7.4-6</t>
         </is>
       </c>
       <c r="B621" s="7" t="inlineStr">
@@ -38682,7 +38693,7 @@
       </c>
       <c r="C621" s="5" t="inlineStr">
         <is>
-          <t>Verify Switch Firmware Component IDs (Tc7.4-7, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET FirmwareInventory/{id} - Individual Entry (Tc7.4-6, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -38697,7 +38708,7 @@
       </c>
       <c r="H621" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I621" s="21" t="inlineStr">
@@ -38724,7 +38735,7 @@
     <row r="622" ht="32" customHeight="1" s="33">
       <c r="A622" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.4-8</t>
+          <t>TC-BLT-7.4-7</t>
         </is>
       </c>
       <c r="B622" s="7" t="inlineStr">
@@ -38734,7 +38745,7 @@
       </c>
       <c r="C622" s="5" t="inlineStr">
         <is>
-          <t>Verify All Entries Accessible (Tc7.4-8, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Switch Firmware Component IDs (Tc7.4-7, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -38749,7 +38760,7 @@
       </c>
       <c r="H622" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I622" s="21" t="inlineStr">
@@ -38776,7 +38787,7 @@
     <row r="623" ht="32" customHeight="1" s="33">
       <c r="A623" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.4-11</t>
+          <t>TC-BLT-7.4-8</t>
         </is>
       </c>
       <c r="B623" s="7" t="inlineStr">
@@ -38786,7 +38797,7 @@
       </c>
       <c r="C623" s="5" t="inlineStr">
         <is>
-          <t>Verify Switch BMC Firmware Entry (Tc7.4-11, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify All Entries Accessible (Tc7.4-8, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -38801,7 +38812,7 @@
       </c>
       <c r="H623" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-11); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I623" s="21" t="inlineStr">
@@ -38828,7 +38839,7 @@
     <row r="624" ht="32" customHeight="1" s="33">
       <c r="A624" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.12-1</t>
+          <t>TC-BLT-7.4-11</t>
         </is>
       </c>
       <c r="B624" s="7" t="inlineStr">
@@ -38838,7 +38849,7 @@
       </c>
       <c r="C624" s="5" t="inlineStr">
         <is>
-          <t>List Ethernet Interfaces (Tc7.2.12-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Switch BMC Firmware Entry (Tc7.4-11, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -38853,7 +38864,7 @@
       </c>
       <c r="H624" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.12-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.4-11); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I624" s="21" t="inlineStr">
@@ -38880,7 +38891,7 @@
     <row r="625" ht="32" customHeight="1" s="33">
       <c r="A625" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.12-2</t>
+          <t>TC-BLT-7.2.12-1</t>
         </is>
       </c>
       <c r="B625" s="7" t="inlineStr">
@@ -38890,7 +38901,7 @@
       </c>
       <c r="C625" s="5" t="inlineStr">
         <is>
-          <t>Get eth0 Details (Tc7.2.12-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Ethernet Interfaces (Tc7.2.12-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -38905,7 +38916,7 @@
       </c>
       <c r="H625" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.12-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.12-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I625" s="21" t="inlineStr">
@@ -38932,7 +38943,7 @@
     <row r="626" ht="32" customHeight="1" s="33">
       <c r="A626" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.13-1</t>
+          <t>TC-BLT-7.2.12-2</t>
         </is>
       </c>
       <c r="B626" s="7" t="inlineStr">
@@ -38942,7 +38953,7 @@
       </c>
       <c r="C626" s="5" t="inlineStr">
         <is>
-          <t>CertificateService Root (Tc7.2.13-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Get eth0 Details (Tc7.2.12-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -38957,7 +38968,7 @@
       </c>
       <c r="H626" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.12-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I626" s="21" t="inlineStr">
@@ -38984,7 +38995,7 @@
     <row r="627" ht="32" customHeight="1" s="33">
       <c r="A627" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.13-2</t>
+          <t>TC-BLT-7.2.13-1</t>
         </is>
       </c>
       <c r="B627" s="7" t="inlineStr">
@@ -38994,7 +39005,7 @@
       </c>
       <c r="C627" s="5" t="inlineStr">
         <is>
-          <t>HTTPS Certificates (Tc7.2.13-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>CertificateService Root (Tc7.2.13-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -39009,7 +39020,7 @@
       </c>
       <c r="H627" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I627" s="21" t="inlineStr">
@@ -39036,7 +39047,7 @@
     <row r="628" ht="32" customHeight="1" s="33">
       <c r="A628" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.13-3</t>
+          <t>TC-BLT-7.2.13-2</t>
         </is>
       </c>
       <c r="B628" s="7" t="inlineStr">
@@ -39046,7 +39057,7 @@
       </c>
       <c r="C628" s="5" t="inlineStr">
         <is>
-          <t>GET Individual Certificate - Active TLS Certificate (Tc7.2.13-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>HTTPS Certificates (Tc7.2.13-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -39061,7 +39072,7 @@
       </c>
       <c r="H628" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I628" s="21" t="inlineStr">
@@ -39088,7 +39099,7 @@
     <row r="629" ht="32" customHeight="1" s="33">
       <c r="A629" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.13-6</t>
+          <t>TC-BLT-7.2.13-3</t>
         </is>
       </c>
       <c r="B629" s="7" t="inlineStr">
@@ -39098,7 +39109,7 @@
       </c>
       <c r="C629" s="5" t="inlineStr">
         <is>
-          <t>Verify ReplaceCertificate Action Target URI Format (Tc7.2.13-6, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Individual Certificate - Active TLS Certificate (Tc7.2.13-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -39113,7 +39124,7 @@
       </c>
       <c r="H629" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I629" s="21" t="inlineStr">
@@ -39140,7 +39151,7 @@
     <row r="630" ht="32" customHeight="1" s="33">
       <c r="A630" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.13-7</t>
+          <t>TC-BLT-7.2.13-6</t>
         </is>
       </c>
       <c r="B630" s="7" t="inlineStr">
@@ -39150,7 +39161,7 @@
       </c>
       <c r="C630" s="5" t="inlineStr">
         <is>
-          <t>Verify Certificate Validity Period (Tc7.2.13-7, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify ReplaceCertificate Action Target URI Format (Tc7.2.13-6, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -39165,7 +39176,7 @@
       </c>
       <c r="H630" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I630" s="21" t="inlineStr">
@@ -39192,7 +39203,7 @@
     <row r="631" ht="32" customHeight="1" s="33">
       <c r="A631" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-1</t>
+          <t>TC-BLT-7.2.13-7</t>
         </is>
       </c>
       <c r="B631" s="7" t="inlineStr">
@@ -39202,7 +39213,7 @@
       </c>
       <c r="C631" s="5" t="inlineStr">
         <is>
-          <t>GET TaskService - Configuration (Tc7.2.14-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Certificate Validity Period (Tc7.2.13-7, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -39217,7 +39228,7 @@
       </c>
       <c r="H631" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.13-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I631" s="21" t="inlineStr">
@@ -39244,7 +39255,7 @@
     <row r="632" ht="32" customHeight="1" s="33">
       <c r="A632" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-2</t>
+          <t>TC-BLT-7.2.14-1</t>
         </is>
       </c>
       <c r="B632" s="7" t="inlineStr">
@@ -39254,7 +39265,7 @@
       </c>
       <c r="C632" s="5" t="inlineStr">
         <is>
-          <t>GET Tasks Collection (Tc7.2.14-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET TaskService - Configuration (Tc7.2.14-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -39269,7 +39280,7 @@
       </c>
       <c r="H632" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I632" s="21" t="inlineStr">
@@ -39296,7 +39307,7 @@
     <row r="633" ht="32" customHeight="1" s="33">
       <c r="A633" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-3</t>
+          <t>TC-BLT-7.2.14-2</t>
         </is>
       </c>
       <c r="B633" s="7" t="inlineStr">
@@ -39306,7 +39317,7 @@
       </c>
       <c r="C633" s="5" t="inlineStr">
         <is>
-          <t>GET Individual Task - Required Fields (Tc7.2.14-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Tasks Collection (Tc7.2.14-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -39321,7 +39332,7 @@
       </c>
       <c r="H633" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I633" s="21" t="inlineStr">
@@ -39348,7 +39359,7 @@
     <row r="634" ht="32" customHeight="1" s="33">
       <c r="A634" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-6</t>
+          <t>TC-BLT-7.2.14-3</t>
         </is>
       </c>
       <c r="B634" s="7" t="inlineStr">
@@ -39358,7 +39369,7 @@
       </c>
       <c r="C634" s="5" t="inlineStr">
         <is>
-          <t>Task StartTime and EndTime Fields (Tc7.2.14-6, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Individual Task - Required Fields (Tc7.2.14-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -39373,7 +39384,7 @@
       </c>
       <c r="H634" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I634" s="21" t="inlineStr">
@@ -39400,7 +39411,7 @@
     <row r="635" ht="32" customHeight="1" s="33">
       <c r="A635" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-8</t>
+          <t>TC-BLT-7.2.14-6</t>
         </is>
       </c>
       <c r="B635" s="7" t="inlineStr">
@@ -39410,7 +39421,7 @@
       </c>
       <c r="C635" s="5" t="inlineStr">
         <is>
-          <t>Task Messages Array Content (Tc7.2.14-8, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Task StartTime and EndTime Fields (Tc7.2.14-6, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -39425,7 +39436,7 @@
       </c>
       <c r="H635" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I635" s="21" t="inlineStr">
@@ -39452,7 +39463,7 @@
     <row r="636" ht="32" customHeight="1" s="33">
       <c r="A636" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-9</t>
+          <t>TC-BLT-7.2.14-8</t>
         </is>
       </c>
       <c r="B636" s="7" t="inlineStr">
@@ -39462,7 +39473,7 @@
       </c>
       <c r="C636" s="5" t="inlineStr">
         <is>
-          <t>GET TelemetryService - Configuration (Tc7.2.14-9, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Task Messages Array Content (Tc7.2.14-8, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -39477,7 +39488,7 @@
       </c>
       <c r="H636" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-9); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I636" s="21" t="inlineStr">
@@ -39504,7 +39515,7 @@
     <row r="637" ht="32" customHeight="1" s="33">
       <c r="A637" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-11</t>
+          <t>TC-BLT-7.2.14-9</t>
         </is>
       </c>
       <c r="B637" s="7" t="inlineStr">
@@ -39514,7 +39525,7 @@
       </c>
       <c r="C637" s="5" t="inlineStr">
         <is>
-          <t>GET MetricDefinitions - Collection (Tc7.2.14-11, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET TelemetryService - Configuration (Tc7.2.14-9, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -39529,7 +39540,7 @@
       </c>
       <c r="H637" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-11); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-9); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I637" s="21" t="inlineStr">
@@ -39556,7 +39567,7 @@
     <row r="638" ht="32" customHeight="1" s="33">
       <c r="A638" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-12</t>
+          <t>TC-BLT-7.2.14-11</t>
         </is>
       </c>
       <c r="B638" s="7" t="inlineStr">
@@ -39566,7 +39577,7 @@
       </c>
       <c r="C638" s="5" t="inlineStr">
         <is>
-          <t>GET MetricDefinitions/{id} - Individual Definition (Tc7.2.14-12, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricDefinitions - Collection (Tc7.2.14-11, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -39581,7 +39592,7 @@
       </c>
       <c r="H638" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-12); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-11); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I638" s="21" t="inlineStr">
@@ -39608,7 +39619,7 @@
     <row r="639" ht="32" customHeight="1" s="33">
       <c r="A639" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-13</t>
+          <t>TC-BLT-7.2.14-12</t>
         </is>
       </c>
       <c r="B639" s="7" t="inlineStr">
@@ -39618,7 +39629,7 @@
       </c>
       <c r="C639" s="5" t="inlineStr">
         <is>
-          <t>GET MetricReportDefinitions - Collection (Tc7.2.14-13, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricDefinitions/{id} - Individual Definition (Tc7.2.14-12, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -39633,7 +39644,7 @@
       </c>
       <c r="H639" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-12); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I639" s="21" t="inlineStr">
@@ -39660,7 +39671,7 @@
     <row r="640" ht="32" customHeight="1" s="33">
       <c r="A640" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-16</t>
+          <t>TC-BLT-7.2.14-13</t>
         </is>
       </c>
       <c r="B640" s="7" t="inlineStr">
@@ -39670,7 +39681,7 @@
       </c>
       <c r="C640" s="5" t="inlineStr">
         <is>
-          <t>GET MetricReports - Collection (Tc7.2.14-16, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricReportDefinitions - Collection (Tc7.2.14-13, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -39685,7 +39696,7 @@
       </c>
       <c r="H640" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-16); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I640" s="21" t="inlineStr">
@@ -39712,7 +39723,7 @@
     <row r="641" ht="32" customHeight="1" s="33">
       <c r="A641" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-17</t>
+          <t>TC-BLT-7.2.14-16</t>
         </is>
       </c>
       <c r="B641" s="7" t="inlineStr">
@@ -39722,7 +39733,7 @@
       </c>
       <c r="C641" s="5" t="inlineStr">
         <is>
-          <t>GET MetricReports/{id} - Individual Report (Tc7.2.14-17, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricReports - Collection (Tc7.2.14-16, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -39737,7 +39748,7 @@
       </c>
       <c r="H641" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-17); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-16); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I641" s="21" t="inlineStr">
@@ -39764,7 +39775,7 @@
     <row r="642" ht="32" customHeight="1" s="33">
       <c r="A642" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-19</t>
+          <t>TC-BLT-7.2.14-17</t>
         </is>
       </c>
       <c r="B642" s="7" t="inlineStr">
@@ -39774,7 +39785,7 @@
       </c>
       <c r="C642" s="5" t="inlineStr">
         <is>
-          <t>TelemetryService Structure Verified (Tc7.2.14-19, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricReports/{id} - Individual Report (Tc7.2.14-17, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -39789,7 +39800,7 @@
       </c>
       <c r="H642" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-19); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-17); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I642" s="21" t="inlineStr">
@@ -39816,7 +39827,7 @@
     <row r="643" ht="32" customHeight="1" s="33">
       <c r="A643" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-20</t>
+          <t>TC-BLT-7.2.14-19</t>
         </is>
       </c>
       <c r="B643" s="7" t="inlineStr">
@@ -39826,7 +39837,7 @@
       </c>
       <c r="C643" s="5" t="inlineStr">
         <is>
-          <t>MetricDefinitions Auto-Populated (Tc7.2.14-20, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>TelemetryService Structure Verified (Tc7.2.14-19, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -39841,7 +39852,7 @@
       </c>
       <c r="H643" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-20); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-19); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I643" s="21" t="inlineStr">
@@ -39868,7 +39879,7 @@
     <row r="644" ht="32" customHeight="1" s="33">
       <c r="A644" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-21</t>
+          <t>TC-BLT-7.2.14-20</t>
         </is>
       </c>
       <c r="B644" s="7" t="inlineStr">
@@ -39878,7 +39889,7 @@
       </c>
       <c r="C644" s="5" t="inlineStr">
         <is>
-          <t>Deduplication Keys Present (Tc7.2.14-21, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>MetricDefinitions Auto-Populated (Tc7.2.14-20, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -39893,7 +39904,7 @@
       </c>
       <c r="H644" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-21); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-20); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I644" s="21" t="inlineStr">
@@ -39920,7 +39931,7 @@
     <row r="645" ht="32" customHeight="1" s="33">
       <c r="A645" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-22</t>
+          <t>TC-BLT-7.2.14-21</t>
         </is>
       </c>
       <c r="B645" s="7" t="inlineStr">
@@ -39930,7 +39941,7 @@
       </c>
       <c r="C645" s="5" t="inlineStr">
         <is>
-          <t>MetricProperties Lists Switch Sensor URIs (Tc7.2.14-22, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Deduplication Keys Present (Tc7.2.14-21, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -39945,7 +39956,7 @@
       </c>
       <c r="H645" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-22); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-21); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I645" s="21" t="inlineStr">
@@ -39972,7 +39983,7 @@
     <row r="646" ht="32" customHeight="1" s="33">
       <c r="A646" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.14-23</t>
+          <t>TC-BLT-7.2.14-22</t>
         </is>
       </c>
       <c r="B646" s="7" t="inlineStr">
@@ -39982,7 +39993,7 @@
       </c>
       <c r="C646" s="5" t="inlineStr">
         <is>
-          <t>Client Workflow - Browse (Tc7.2.14-23, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>MetricProperties Lists Switch Sensor URIs (Tc7.2.14-22, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -39997,7 +40008,7 @@
       </c>
       <c r="H646" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-23); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-22); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I646" s="21" t="inlineStr">
@@ -40024,7 +40035,7 @@
     <row r="647" ht="32" customHeight="1" s="33">
       <c r="A647" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-4</t>
+          <t>TC-BLT-7.2.14-23</t>
         </is>
       </c>
       <c r="B647" s="7" t="inlineStr">
@@ -40034,7 +40045,7 @@
       </c>
       <c r="C647" s="5" t="inlineStr">
         <is>
-          <t>TelemetryService Structure Verified (Tc7.5.9-4, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Client Workflow - Browse (Tc7.2.14-23, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -40049,7 +40060,7 @@
       </c>
       <c r="H647" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-4); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.14-23); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I647" s="21" t="inlineStr">
@@ -40076,7 +40087,7 @@
     <row r="648" ht="32" customHeight="1" s="33">
       <c r="A648" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-5</t>
+          <t>TC-BLT-7.5.9-4</t>
         </is>
       </c>
       <c r="B648" s="7" t="inlineStr">
@@ -40086,7 +40097,7 @@
       </c>
       <c r="C648" s="5" t="inlineStr">
         <is>
-          <t>Deduplication Keys Present (Tc7.5.9-5, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>TelemetryService Structure Verified (Tc7.5.9-4, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -40101,7 +40112,7 @@
       </c>
       <c r="H648" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-5); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-4); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I648" s="21" t="inlineStr">
@@ -40128,7 +40139,7 @@
     <row r="649" ht="32" customHeight="1" s="33">
       <c r="A649" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-6</t>
+          <t>TC-BLT-7.5.9-5</t>
         </is>
       </c>
       <c r="B649" s="7" t="inlineStr">
@@ -40138,7 +40149,7 @@
       </c>
       <c r="C649" s="5" t="inlineStr">
         <is>
-          <t>MetricProperties Lists Switch Sensor URIs (Tc7.5.9-6, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Deduplication Keys Present (Tc7.5.9-5, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -40153,7 +40164,7 @@
       </c>
       <c r="H649" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-5); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I649" s="21" t="inlineStr">
@@ -40180,7 +40191,7 @@
     <row r="650" ht="32" customHeight="1" s="33">
       <c r="A650" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-7</t>
+          <t>TC-BLT-7.5.9-6</t>
         </is>
       </c>
       <c r="B650" s="7" t="inlineStr">
@@ -40190,7 +40201,7 @@
       </c>
       <c r="C650" s="5" t="inlineStr">
         <is>
-          <t>Client Workflow - Browse (Tc7.5.9-7, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>MetricProperties Lists Switch Sensor URIs (Tc7.5.9-6, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -40205,7 +40216,7 @@
       </c>
       <c r="H650" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-6); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I650" s="21" t="inlineStr">
@@ -40232,7 +40243,7 @@
     <row r="651" ht="32" customHeight="1" s="33">
       <c r="A651" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-8</t>
+          <t>TC-BLT-7.5.9-7</t>
         </is>
       </c>
       <c r="B651" s="7" t="inlineStr">
@@ -40242,7 +40253,7 @@
       </c>
       <c r="C651" s="5" t="inlineStr">
         <is>
-          <t>Client Workflow - Pick and Review MetricProperties (Tc7.5.9-8, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Client Workflow - Browse (Tc7.5.9-7, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -40257,7 +40268,7 @@
       </c>
       <c r="H651" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I651" s="21" t="inlineStr">
@@ -40284,7 +40295,7 @@
     <row r="652" ht="32" customHeight="1" s="33">
       <c r="A652" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-13</t>
+          <t>TC-BLT-7.5.9-8</t>
         </is>
       </c>
       <c r="B652" s="7" t="inlineStr">
@@ -40294,7 +40305,7 @@
       </c>
       <c r="C652" s="5" t="inlineStr">
         <is>
-          <t>GET MetricReports - Collection (Tc7.5.9-13, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Client Workflow - Pick and Review MetricProperties (Tc7.5.9-8, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -40309,7 +40320,7 @@
       </c>
       <c r="H652" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-8); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I652" s="21" t="inlineStr">
@@ -40336,7 +40347,7 @@
     <row r="653" ht="32" customHeight="1" s="33">
       <c r="A653" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-14</t>
+          <t>TC-BLT-7.5.9-13</t>
         </is>
       </c>
       <c r="B653" s="7" t="inlineStr">
@@ -40346,7 +40357,7 @@
       </c>
       <c r="C653" s="5" t="inlineStr">
         <is>
-          <t>GET MetricReports/{id} (Tc7.5.9-14, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricReports - Collection (Tc7.5.9-13, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -40361,7 +40372,7 @@
       </c>
       <c r="H653" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-13); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I653" s="21" t="inlineStr">
@@ -40388,7 +40399,7 @@
     <row r="654" ht="32" customHeight="1" s="33">
       <c r="A654" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.1-1</t>
+          <t>TC-BLT-7.5.9-14</t>
         </is>
       </c>
       <c r="B654" s="7" t="inlineStr">
@@ -40398,7 +40409,7 @@
       </c>
       <c r="C654" s="5" t="inlineStr">
         <is>
-          <t>Service Root &amp; Version (Tc7.3.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET MetricReports/{id} (Tc7.5.9-14, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -40413,7 +40424,7 @@
       </c>
       <c r="H654" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-14); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I654" s="21" t="inlineStr">
@@ -40440,7 +40451,7 @@
     <row r="655" ht="32" customHeight="1" s="33">
       <c r="A655" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.1-2</t>
+          <t>TC-BLT-7.3.1-1</t>
         </is>
       </c>
       <c r="B655" s="7" t="inlineStr">
@@ -40450,7 +40461,7 @@
       </c>
       <c r="C655" s="5" t="inlineStr">
         <is>
-          <t>Managers &amp; NetworkProtocol (Tc7.3.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Service Root &amp; Version (Tc7.3.1-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -40465,7 +40476,7 @@
       </c>
       <c r="H655" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I655" s="21" t="inlineStr">
@@ -40492,7 +40503,7 @@
     <row r="656" ht="32" customHeight="1" s="33">
       <c r="A656" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.1-3</t>
+          <t>TC-BLT-7.3.1-2</t>
         </is>
       </c>
       <c r="B656" s="7" t="inlineStr">
@@ -40502,7 +40513,7 @@
       </c>
       <c r="C656" s="5" t="inlineStr">
         <is>
-          <t>EthernetInterfaces (eth0) (Tc7.3.1-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Managers &amp; NetworkProtocol (Tc7.3.1-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -40517,7 +40528,7 @@
       </c>
       <c r="H656" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I656" s="21" t="inlineStr">
@@ -40544,7 +40555,7 @@
     <row r="657" ht="32" customHeight="1" s="33">
       <c r="A657" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.4-1</t>
+          <t>TC-BLT-7.3.1-3</t>
         </is>
       </c>
       <c r="B657" s="7" t="inlineStr">
@@ -40554,7 +40565,7 @@
       </c>
       <c r="C657" s="5" t="inlineStr">
         <is>
-          <t>Journal &amp; SEL LogServices (Tc7.3.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>EthernetInterfaces (eth0) (Tc7.3.1-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -40569,7 +40580,7 @@
       </c>
       <c r="H657" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.1-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I657" s="21" t="inlineStr">
@@ -40596,7 +40607,7 @@
     <row r="658" ht="32" customHeight="1" s="33">
       <c r="A658" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.5-1</t>
+          <t>TC-BLT-7.3.4-1</t>
         </is>
       </c>
       <c r="B658" s="7" t="inlineStr">
@@ -40606,7 +40617,7 @@
       </c>
       <c r="C658" s="5" t="inlineStr">
         <is>
-          <t>Authentication &amp; TLS Enforcement (Tc7.3.5-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Journal &amp; SEL LogServices (Tc7.3.4-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -40621,7 +40632,7 @@
       </c>
       <c r="H658" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.5-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.4-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I658" s="21" t="inlineStr">
@@ -40648,7 +40659,7 @@
     <row r="659" ht="32" customHeight="1" s="33">
       <c r="A659" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.6-1</t>
+          <t>TC-BLT-7.3.5-1</t>
         </is>
       </c>
       <c r="B659" s="7" t="inlineStr">
@@ -40658,7 +40669,7 @@
       </c>
       <c r="C659" s="5" t="inlineStr">
         <is>
-          <t>Sensor Discovery (D-Bus &amp; Redfish) (Tc7.3.6-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Authentication &amp; TLS Enforcement (Tc7.3.5-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -40673,7 +40684,7 @@
       </c>
       <c r="H659" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.6-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.5-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I659" s="21" t="inlineStr">
@@ -40700,7 +40711,7 @@
     <row r="660" ht="32" customHeight="1" s="33">
       <c r="A660" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.3.6-2</t>
+          <t>TC-BLT-7.3.6-1</t>
         </is>
       </c>
       <c r="B660" s="7" t="inlineStr">
@@ -40710,7 +40721,7 @@
       </c>
       <c r="C660" s="5" t="inlineStr">
         <is>
-          <t>Threshold &amp; Health Mapping (Tc7.3.6-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Sensor Discovery (D-Bus &amp; Redfish) (Tc7.3.6-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -40725,7 +40736,7 @@
       </c>
       <c r="H660" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.6-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.6-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I660" s="21" t="inlineStr">
@@ -40752,7 +40763,7 @@
     <row r="661" ht="32" customHeight="1" s="33">
       <c r="A661" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.13-1</t>
+          <t>TC-BLT-7.3.6-2</t>
         </is>
       </c>
       <c r="B661" s="7" t="inlineStr">
@@ -40762,7 +40773,7 @@
       </c>
       <c r="C661" s="5" t="inlineStr">
         <is>
-          <t>GET ServiceConditions - Root Resource (Tc7.5.13-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Threshold &amp; Health Mapping (Tc7.3.6-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -40777,7 +40788,7 @@
       </c>
       <c r="H661" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.3.6-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I661" s="21" t="inlineStr">
@@ -40804,7 +40815,7 @@
     <row r="662" ht="32" customHeight="1" s="33">
       <c r="A662" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.13-2</t>
+          <t>TC-BLT-7.5.13-1</t>
         </is>
       </c>
       <c r="B662" s="7" t="inlineStr">
@@ -40814,7 +40825,7 @@
       </c>
       <c r="C662" s="5" t="inlineStr">
         <is>
-          <t>Verify Condition Object Structure (Tc7.5.13-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET ServiceConditions - Root Resource (Tc7.5.13-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -40829,7 +40840,7 @@
       </c>
       <c r="H662" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-1); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I662" s="21" t="inlineStr">
@@ -40856,7 +40867,7 @@
     <row r="663" ht="32" customHeight="1" s="33">
       <c r="A663" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.13-3</t>
+          <t>TC-BLT-7.5.13-2</t>
         </is>
       </c>
       <c r="B663" s="7" t="inlineStr">
@@ -40866,7 +40877,7 @@
       </c>
       <c r="C663" s="5" t="inlineStr">
         <is>
-          <t>Verify Severity Values (Tc7.5.13-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Condition Object Structure (Tc7.5.13-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -40881,7 +40892,7 @@
       </c>
       <c r="H663" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-2); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I663" s="21" t="inlineStr">
@@ -40908,7 +40919,7 @@
     <row r="664" ht="32" customHeight="1" s="33">
       <c r="A664" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.13-4</t>
+          <t>TC-BLT-7.5.13-3</t>
         </is>
       </c>
       <c r="B664" s="7" t="inlineStr">
@@ -40918,7 +40929,7 @@
       </c>
       <c r="C664" s="5" t="inlineStr">
         <is>
-          <t>Verify OriginOfCondition URIs (Tc7.5.13-4, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Severity Values (Tc7.5.13-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -40933,7 +40944,7 @@
       </c>
       <c r="H664" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-4); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-3); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I664" s="21" t="inlineStr">
@@ -40960,7 +40971,7 @@
     <row r="665" ht="32" customHeight="1" s="33">
       <c r="A665" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.13-5</t>
+          <t>TC-BLT-7.5.13-4</t>
         </is>
       </c>
       <c r="B665" s="7" t="inlineStr">
@@ -40970,7 +40981,7 @@
       </c>
       <c r="C665" s="5" t="inlineStr">
         <is>
-          <t>Verify Timestamp Format (Tc7.5.13-5, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify OriginOfCondition URIs (Tc7.5.13-4, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -40985,7 +40996,7 @@
       </c>
       <c r="H665" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-5); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-4); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I665" s="21" t="inlineStr">
@@ -41012,7 +41023,7 @@
     <row r="666" ht="32" customHeight="1" s="33">
       <c r="A666" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.13-7</t>
+          <t>TC-BLT-7.5.13-5</t>
         </is>
       </c>
       <c r="B666" s="7" t="inlineStr">
@@ -41022,7 +41033,7 @@
       </c>
       <c r="C666" s="5" t="inlineStr">
         <is>
-          <t>Client Workflow - Poll, Identify, Filter (Tc7.5.13-7, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Timestamp Format (Tc7.5.13-5, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -41037,7 +41048,7 @@
       </c>
       <c r="H666" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-5); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I666" s="21" t="inlineStr">
@@ -41064,7 +41075,7 @@
     <row r="667" ht="32" customHeight="1" s="33">
       <c r="A667" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-1</t>
+          <t>TC-BLT-7.5.13-7</t>
         </is>
       </c>
       <c r="B667" s="7" t="inlineStr">
@@ -41074,7 +41085,7 @@
       </c>
       <c r="C667" s="5" t="inlineStr">
         <is>
-          <t>USB Presence Detection ['check'] (Tc7.1.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Client Workflow - Poll, Identify, Filter (Tc7.5.13-7, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -41089,12 +41100,12 @@
       </c>
       <c r="H667" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.13-7); automated read-only in tests/bmc/test_blanton_redfish.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI)</t>
         </is>
       </c>
       <c r="I667" s="21" t="inlineStr">
         <is>
-          <t>Switch SSH (bmc-manager.sh, sudo)</t>
+          <t>Switch BMC Redfish (HTTPS)</t>
         </is>
       </c>
       <c r="J667" s="21" t="inlineStr">
@@ -41116,7 +41127,7 @@
     <row r="668" ht="32" customHeight="1" s="33">
       <c r="A668" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-2</t>
+          <t>TC-BLT-7.1.1-1</t>
         </is>
       </c>
       <c r="B668" s="7" t="inlineStr">
@@ -41126,7 +41137,7 @@
       </c>
       <c r="C668" s="5" t="inlineStr">
         <is>
-          <t>Help Menu ['--help' | '-h'] (Tc7.1.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>USB Presence Detection ['check'] (Tc7.1.1-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -41141,7 +41152,7 @@
       </c>
       <c r="H668" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-2); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I668" s="21" t="inlineStr">
@@ -41168,7 +41179,7 @@
     <row r="669" ht="32" customHeight="1" s="33">
       <c r="A669" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-4</t>
+          <t>TC-BLT-7.1.1-2</t>
         </is>
       </c>
       <c r="B669" s="7" t="inlineStr">
@@ -41178,7 +41189,7 @@
       </c>
       <c r="C669" s="5" t="inlineStr">
         <is>
-          <t>Display Version Information ['version'] (Tc7.1.1-4, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Help Menu ['--help' | '-h'] (Tc7.1.1-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -41193,7 +41204,7 @@
       </c>
       <c r="H669" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-4); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-2); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I669" s="21" t="inlineStr">
@@ -41220,7 +41231,7 @@
     <row r="670" ht="32" customHeight="1" s="33">
       <c r="A670" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-5</t>
+          <t>TC-BLT-7.1.1-4</t>
         </is>
       </c>
       <c r="B670" s="7" t="inlineStr">
@@ -41230,7 +41241,7 @@
       </c>
       <c r="C670" s="5" t="inlineStr">
         <is>
-          <t>System Status Overview ['status'] (Tc7.1.1-5, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Display Version Information ['version'] (Tc7.1.1-4, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -41245,7 +41256,7 @@
       </c>
       <c r="H670" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-5); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-4); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I670" s="21" t="inlineStr">
@@ -41272,7 +41283,7 @@
     <row r="671" ht="32" customHeight="1" s="33">
       <c r="A671" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-6</t>
+          <t>TC-BLT-7.1.1-5</t>
         </is>
       </c>
       <c r="B671" s="7" t="inlineStr">
@@ -41282,7 +41293,7 @@
       </c>
       <c r="C671" s="5" t="inlineStr">
         <is>
-          <t>Health Check ['health'] (Tc7.1.1-6, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>System Status Overview ['status'] (Tc7.1.1-5, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -41297,7 +41308,7 @@
       </c>
       <c r="H671" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-6); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-5); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I671" s="21" t="inlineStr">
@@ -41324,7 +41335,7 @@
     <row r="672" ht="32" customHeight="1" s="33">
       <c r="A672" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-9</t>
+          <t>TC-BLT-7.1.1-6</t>
         </is>
       </c>
       <c r="B672" s="7" t="inlineStr">
@@ -41334,7 +41345,7 @@
       </c>
       <c r="C672" s="5" t="inlineStr">
         <is>
-          <t>Default Boot Flash ('flash-info') (Tc7.1.1-9, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Health Check ['health'] (Tc7.1.1-6, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -41349,7 +41360,7 @@
       </c>
       <c r="H672" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-9); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-6); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I672" s="21" t="inlineStr">
@@ -41376,7 +41387,7 @@
     <row r="673" ht="32" customHeight="1" s="33">
       <c r="A673" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.1-10</t>
+          <t>TC-BLT-7.1.1-9</t>
         </is>
       </c>
       <c r="B673" s="7" t="inlineStr">
@@ -41386,7 +41397,7 @@
       </c>
       <c r="C673" s="5" t="inlineStr">
         <is>
-          <t>Flash Partition Information ['flash-info'] (Tc7.1.1-10, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Default Boot Flash ('flash-info') (Tc7.1.1-9, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -41401,7 +41412,7 @@
       </c>
       <c r="H673" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-10); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-9); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I673" s="21" t="inlineStr">
@@ -41428,7 +41439,7 @@
     <row r="674" ht="32" customHeight="1" s="33">
       <c r="A674" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.2-1</t>
+          <t>TC-BLT-7.1.1-10</t>
         </is>
       </c>
       <c r="B674" s="7" t="inlineStr">
@@ -41438,7 +41449,7 @@
       </c>
       <c r="C674" s="5" t="inlineStr">
         <is>
-          <t>Journal Streaming [No Filter |errors |warnings |boot |] (Tc7.1.2-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Flash Partition Information ['flash-info'] (Tc7.1.1-10, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -41453,7 +41464,7 @@
       </c>
       <c r="H674" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.2-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.1-10); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I674" s="21" t="inlineStr">
@@ -41480,7 +41491,7 @@
     <row r="675" ht="32" customHeight="1" s="33">
       <c r="A675" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.2-2</t>
+          <t>TC-BLT-7.1.2-1</t>
         </is>
       </c>
       <c r="B675" s="7" t="inlineStr">
@@ -41490,7 +41501,7 @@
       </c>
       <c r="C675" s="5" t="inlineStr">
         <is>
-          <t>Kernel Logs ['dmesg'] (Tc7.1.2-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Journal Streaming [No Filter |errors |warnings |boot |] (Tc7.1.2-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -41505,7 +41516,7 @@
       </c>
       <c r="H675" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.2-2); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.2-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I675" s="21" t="inlineStr">
@@ -41532,7 +41543,7 @@
     <row r="676" ht="32" customHeight="1" s="33">
       <c r="A676" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.3-3</t>
+          <t>TC-BLT-7.1.2-2</t>
         </is>
       </c>
       <c r="B676" s="7" t="inlineStr">
@@ -41542,7 +41553,7 @@
       </c>
       <c r="C676" s="5" t="inlineStr">
         <is>
-          <t>Check SSH Access Status ['ssh-access status'] (Tc7.1.3-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Kernel Logs ['dmesg'] (Tc7.1.2-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -41557,7 +41568,7 @@
       </c>
       <c r="H676" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.3-3); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.2-2); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I676" s="21" t="inlineStr">
@@ -41584,7 +41595,7 @@
     <row r="677" ht="32" customHeight="1" s="33">
       <c r="A677" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.1.4-1</t>
+          <t>TC-BLT-7.1.3-3</t>
         </is>
       </c>
       <c r="B677" s="7" t="inlineStr">
@@ -41594,7 +41605,7 @@
       </c>
       <c r="C677" s="5" t="inlineStr">
         <is>
-          <t>List Configuration Files ['config-list'] (Tc7.1.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Check SSH Access Status ['ssh-access status'] (Tc7.1.3-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -41609,7 +41620,7 @@
       </c>
       <c r="H677" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.4-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.3-3); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I677" s="21" t="inlineStr">
@@ -41636,7 +41647,7 @@
     <row r="678" ht="32" customHeight="1" s="33">
       <c r="A678" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.6-17</t>
+          <t>TC-BLT-7.1.4-1</t>
         </is>
       </c>
       <c r="B678" s="7" t="inlineStr">
@@ -41646,7 +41657,7 @@
       </c>
       <c r="C678" s="5" t="inlineStr">
         <is>
-          <t>Verify redfish docker container is only enabled on liquid cooling platforms. (Tc7.2.6-17, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Configuration Files ['config-list'] (Tc7.1.4-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -41661,7 +41672,7 @@
       </c>
       <c r="H678" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-17); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.1.4-1); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I678" s="21" t="inlineStr">
@@ -41688,7 +41699,7 @@
     <row r="679" ht="32" customHeight="1" s="33">
       <c r="A679" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.2.6-19</t>
+          <t>TC-BLT-7.2.6-17</t>
         </is>
       </c>
       <c r="B679" s="7" t="inlineStr">
@@ -41698,7 +41709,7 @@
       </c>
       <c r="C679" s="5" t="inlineStr">
         <is>
-          <t>Rack Manager Reachability - REACHABLE (Tc7.2.6-19, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify redfish docker container is only enabled on liquid cooling platforms. (Tc7.2.6-17, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -41713,7 +41724,7 @@
       </c>
       <c r="H679" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-19); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-17); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I679" s="21" t="inlineStr">
@@ -41740,7 +41751,7 @@
     <row r="680" ht="32" customHeight="1" s="33">
       <c r="A680" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.1-1</t>
+          <t>TC-BLT-7.2.6-19</t>
         </is>
       </c>
       <c r="B680" s="7" t="inlineStr">
@@ -41750,7 +41761,7 @@
       </c>
       <c r="C680" s="5" t="inlineStr">
         <is>
-          <t>GET Aggregator Service Root (Tc7.5.1-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Rack Manager Reachability - REACHABLE (Tc7.2.6-19, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -41765,17 +41776,17 @@
       </c>
       <c r="H680" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.2.6-19); automated read-only in tests/bmc/test_blanton_cli.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); bmc-manager.sh on the switch</t>
         </is>
       </c>
       <c r="I680" s="21" t="inlineStr">
         <is>
-          <t>ARIM Redfish (HTTPS)</t>
+          <t>Switch SSH (bmc-manager.sh, sudo)</t>
         </is>
       </c>
       <c r="J680" s="21" t="inlineStr">
         <is>
-          <t>BMC (ARIM rack manager)</t>
+          <t>BMC (Switch)</t>
         </is>
       </c>
       <c r="K680" s="21" t="inlineStr">
@@ -41792,7 +41803,7 @@
     <row r="681" ht="32" customHeight="1" s="33">
       <c r="A681" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.1-2</t>
+          <t>TC-BLT-7.5.1-1</t>
         </is>
       </c>
       <c r="B681" s="7" t="inlineStr">
@@ -41802,7 +41813,7 @@
       </c>
       <c r="C681" s="5" t="inlineStr">
         <is>
-          <t>GET /redfish Version Object (Tc7.5.1-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Aggregator Service Root (Tc7.5.1-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -41817,7 +41828,7 @@
       </c>
       <c r="H681" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I681" s="21" t="inlineStr">
@@ -41844,7 +41855,7 @@
     <row r="682" ht="32" customHeight="1" s="33">
       <c r="A682" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.1-3</t>
+          <t>TC-BLT-7.5.1-2</t>
         </is>
       </c>
       <c r="B682" s="7" t="inlineStr">
@@ -41854,7 +41865,7 @@
       </c>
       <c r="C682" s="5" t="inlineStr">
         <is>
-          <t>GET JsonSchemas Collection (Tc7.5.1-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET /redfish Version Object (Tc7.5.1-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -41869,7 +41880,7 @@
       </c>
       <c r="H682" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I682" s="21" t="inlineStr">
@@ -41896,7 +41907,7 @@
     <row r="683" ht="32" customHeight="1" s="33">
       <c r="A683" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.1-4</t>
+          <t>TC-BLT-7.5.1-3</t>
         </is>
       </c>
       <c r="B683" s="7" t="inlineStr">
@@ -41906,7 +41917,7 @@
       </c>
       <c r="C683" s="5" t="inlineStr">
         <is>
-          <t>GET Registries Collection (Tc7.5.1-4, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET JsonSchemas Collection (Tc7.5.1-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -41921,7 +41932,7 @@
       </c>
       <c r="H683" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I683" s="21" t="inlineStr">
@@ -41948,7 +41959,7 @@
     <row r="684" ht="32" customHeight="1" s="33">
       <c r="A684" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.2-4</t>
+          <t>TC-BLT-7.5.1-4</t>
         </is>
       </c>
       <c r="B684" s="7" t="inlineStr">
@@ -41958,7 +41969,7 @@
       </c>
       <c r="C684" s="5" t="inlineStr">
         <is>
-          <t>List Connection Methods (Tc7.5.2-4, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>GET Registries Collection (Tc7.5.1-4, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -41973,7 +41984,7 @@
       </c>
       <c r="H684" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.2-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.1-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I684" s="21" t="inlineStr">
@@ -42000,7 +42011,7 @@
     <row r="685" ht="32" customHeight="1" s="33">
       <c r="A685" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.3-1</t>
+          <t>TC-BLT-7.5.2-4</t>
         </is>
       </c>
       <c r="B685" s="7" t="inlineStr">
@@ -42010,7 +42021,7 @@
       </c>
       <c r="C685" s="5" t="inlineStr">
         <is>
-          <t>Verify Transparent Proxy Rule (Tc7.5.3-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>List Connection Methods (Tc7.5.2-4, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -42025,7 +42036,7 @@
       </c>
       <c r="H685" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.3-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.2-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I685" s="21" t="inlineStr">
@@ -42052,7 +42063,7 @@
     <row r="686" ht="32" customHeight="1" s="33">
       <c r="A686" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.3-2</t>
+          <t>TC-BLT-7.5.3-1</t>
         </is>
       </c>
       <c r="B686" s="7" t="inlineStr">
@@ -42062,7 +42073,7 @@
       </c>
       <c r="C686" s="5" t="inlineStr">
         <is>
-          <t>Verify URI Rewriting in Responses (Tc7.5.3-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify Transparent Proxy Rule (Tc7.5.3-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -42077,7 +42088,7 @@
       </c>
       <c r="H686" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.3-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.3-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I686" s="21" t="inlineStr">
@@ -42104,7 +42115,7 @@
     <row r="687" ht="32" customHeight="1" s="33">
       <c r="A687" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.4-1</t>
+          <t>TC-BLT-7.5.3-2</t>
         </is>
       </c>
       <c r="B687" s="7" t="inlineStr">
@@ -42114,7 +42125,7 @@
       </c>
       <c r="C687" s="5" t="inlineStr">
         <is>
-          <t>Systems Collection Membership (Tc7.5.4-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Verify URI Rewriting in Responses (Tc7.5.3-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -42129,7 +42140,7 @@
       </c>
       <c r="H687" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.3-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I687" s="21" t="inlineStr">
@@ -42156,7 +42167,7 @@
     <row r="688" ht="32" customHeight="1" s="33">
       <c r="A688" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.4-2</t>
+          <t>TC-BLT-7.5.4-1</t>
         </is>
       </c>
       <c r="B688" s="7" t="inlineStr">
@@ -42166,7 +42177,7 @@
       </c>
       <c r="C688" s="5" t="inlineStr">
         <is>
-          <t>Chassis Collection Membership (Tc7.5.4-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Systems Collection Membership (Tc7.5.4-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -42181,7 +42192,7 @@
       </c>
       <c r="H688" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I688" s="21" t="inlineStr">
@@ -42208,7 +42219,7 @@
     <row r="689" ht="32" customHeight="1" s="33">
       <c r="A689" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.4-3</t>
+          <t>TC-BLT-7.5.4-2</t>
         </is>
       </c>
       <c r="B689" s="7" t="inlineStr">
@@ -42218,7 +42229,7 @@
       </c>
       <c r="C689" s="5" t="inlineStr">
         <is>
-          <t>Managers Collection Membership (Tc7.5.4-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Chassis Collection Membership (Tc7.5.4-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -42233,7 +42244,7 @@
       </c>
       <c r="H689" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I689" s="21" t="inlineStr">
@@ -42260,7 +42271,7 @@
     <row r="690" ht="32" customHeight="1" s="33">
       <c r="A690" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.4-4</t>
+          <t>TC-BLT-7.5.4-3</t>
         </is>
       </c>
       <c r="B690" s="7" t="inlineStr">
@@ -42270,7 +42281,7 @@
       </c>
       <c r="C690" s="5" t="inlineStr">
         <is>
-          <t>Chassis Containment Hierarchy (Tc7.5.4-4, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Managers Collection Membership (Tc7.5.4-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -42285,7 +42296,7 @@
       </c>
       <c r="H690" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I690" s="21" t="inlineStr">
@@ -42312,7 +42323,7 @@
     <row r="691" ht="32" customHeight="1" s="33">
       <c r="A691" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.5-1</t>
+          <t>TC-BLT-7.5.4-4</t>
         </is>
       </c>
       <c r="B691" s="7" t="inlineStr">
@@ -42322,7 +42333,7 @@
       </c>
       <c r="C691" s="5" t="inlineStr">
         <is>
-          <t>ComponentIntegrity Collection (Tc7.5.5-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Chassis Containment Hierarchy (Tc7.5.4-4, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -42337,7 +42348,7 @@
       </c>
       <c r="H691" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.5-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.4-4); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I691" s="21" t="inlineStr">
@@ -42364,7 +42375,7 @@
     <row r="692" ht="32" customHeight="1" s="33">
       <c r="A692" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.7-1</t>
+          <t>TC-BLT-7.5.5-1</t>
         </is>
       </c>
       <c r="B692" s="7" t="inlineStr">
@@ -42374,7 +42385,7 @@
       </c>
       <c r="C692" s="5" t="inlineStr">
         <is>
-          <t>PowerEquipment Singleton (Tc7.5.7-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>ComponentIntegrity Collection (Tc7.5.5-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -42389,7 +42400,7 @@
       </c>
       <c r="H692" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.5-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I692" s="21" t="inlineStr">
@@ -42416,7 +42427,7 @@
     <row r="693" ht="32" customHeight="1" s="33">
       <c r="A693" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.7-2</t>
+          <t>TC-BLT-7.5.7-1</t>
         </is>
       </c>
       <c r="B693" s="7" t="inlineStr">
@@ -42426,7 +42437,7 @@
       </c>
       <c r="C693" s="5" t="inlineStr">
         <is>
-          <t>Power Shelf Sub-Resources (Tc7.5.7-2, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>PowerEquipment Singleton (Tc7.5.7-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -42441,7 +42452,7 @@
       </c>
       <c r="H693" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I693" s="21" t="inlineStr">
@@ -42468,7 +42479,7 @@
     <row r="694" ht="32" customHeight="1" s="33">
       <c r="A694" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.7-3</t>
+          <t>TC-BLT-7.5.7-2</t>
         </is>
       </c>
       <c r="B694" s="7" t="inlineStr">
@@ -42478,7 +42489,7 @@
       </c>
       <c r="C694" s="5" t="inlineStr">
         <is>
-          <t>Super Cap Battery Resources (Tc7.5.7-3, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Power Shelf Sub-Resources (Tc7.5.7-2, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -42493,7 +42504,7 @@
       </c>
       <c r="H694" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-2); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I694" s="21" t="inlineStr">
@@ -42520,7 +42531,7 @@
     <row r="695" ht="32" customHeight="1" s="33">
       <c r="A695" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.8-1</t>
+          <t>TC-BLT-7.5.7-3</t>
         </is>
       </c>
       <c r="B695" s="7" t="inlineStr">
@@ -42530,7 +42541,7 @@
       </c>
       <c r="C695" s="5" t="inlineStr">
         <is>
-          <t>EventService Configuration (Tc7.5.8-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Super Cap Battery Resources (Tc7.5.7-3, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -42545,7 +42556,7 @@
       </c>
       <c r="H695" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.8-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.7-3); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I695" s="21" t="inlineStr">
@@ -42572,7 +42583,7 @@
     <row r="696" ht="32" customHeight="1" s="33">
       <c r="A696" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.9-1</t>
+          <t>TC-BLT-7.5.8-1</t>
         </is>
       </c>
       <c r="B696" s="7" t="inlineStr">
@@ -42582,7 +42593,7 @@
       </c>
       <c r="C696" s="5" t="inlineStr">
         <is>
-          <t>Deduplicated MetricDefinitions (Tc7.5.9-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>EventService Configuration (Tc7.5.8-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -42597,7 +42608,7 @@
       </c>
       <c r="H696" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.8-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I696" s="21" t="inlineStr">
@@ -42624,7 +42635,7 @@
     <row r="697" ht="32" customHeight="1" s="33">
       <c r="A697" s="7" t="inlineStr">
         <is>
-          <t>TC-BLT-7.5.10-1</t>
+          <t>TC-BLT-7.5.9-1</t>
         </is>
       </c>
       <c r="B697" s="7" t="inlineStr">
@@ -42634,7 +42645,7 @@
       </c>
       <c r="C697" s="5" t="inlineStr">
         <is>
-          <t>Task Tracking for Async Operations (Tc7.5.10-1, Blanton BMC plan TPI-151974, read-only)</t>
+          <t>Deduplicated MetricDefinitions (Tc7.5.9-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -42649,7 +42660,7 @@
       </c>
       <c r="H697" s="21" t="inlineStr">
         <is>
-          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.10-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.9-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
       <c r="I697" s="21" t="inlineStr">
@@ -42676,57 +42687,109 @@
     <row r="698" ht="32" customHeight="1" s="33">
       <c r="A698" s="7" t="inlineStr">
         <is>
+          <t>TC-BLT-7.5.10-1</t>
+        </is>
+      </c>
+      <c r="B698" s="7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="C698" s="5" t="inlineStr">
+        <is>
+          <t>Task Tracking for Async Operations (Tc7.5.10-1, Blanton BMC plan TPI-151974, read-only)</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H698" s="21" t="inlineStr">
+        <is>
+          <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.10-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
+        </is>
+      </c>
+      <c r="I698" s="21" t="inlineStr">
+        <is>
+          <t>ARIM Redfish (HTTPS)</t>
+        </is>
+      </c>
+      <c r="J698" s="21" t="inlineStr">
+        <is>
+          <t>BMC (ARIM rack manager)</t>
+        </is>
+      </c>
+      <c r="K698" s="21" t="inlineStr">
+        <is>
+          <t>Added - helios-tests (20 Oct 2026)</t>
+        </is>
+      </c>
+      <c r="L698" s="21" t="inlineStr">
+        <is>
+          <t>Non-disruptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="699" ht="32" customHeight="1" s="33">
+      <c r="A699" s="7" t="inlineStr">
+        <is>
           <t>TC-BLT-7.5.11-1</t>
         </is>
       </c>
-      <c r="B698" s="7" t="inlineStr">
+      <c r="B699" s="7" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C698" s="5" t="inlineStr">
+      <c r="C699" s="5" t="inlineStr">
         <is>
           <t>Aggregated FirmwareInventory (Tc7.5.11-1, Blanton BMC plan TPI-151974, read-only)</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="H698" s="21" t="inlineStr">
+      <c r="H699" s="21" t="inlineStr">
         <is>
           <t>Not run yet: added 20 Oct 2026 from Juniper TPI-151974 v1.2 (Blanton BMC plan, Tc7.5.11-1); automated read-only in tests/bmc/test_blanton_arim.py. Needs the switch's bmc / bmc_user in the inventory and its BMC password (UI); an ARIM: arim: {url, user} + $HELIOS_ARIM_PASSWORD</t>
         </is>
       </c>
-      <c r="I698" s="21" t="inlineStr">
+      <c r="I699" s="21" t="inlineStr">
         <is>
           <t>ARIM Redfish (HTTPS)</t>
         </is>
       </c>
-      <c r="J698" s="21" t="inlineStr">
+      <c r="J699" s="21" t="inlineStr">
         <is>
           <t>BMC (ARIM rack manager)</t>
         </is>
       </c>
-      <c r="K698" s="21" t="inlineStr">
+      <c r="K699" s="21" t="inlineStr">
         <is>
           <t>Added - helios-tests (20 Oct 2026)</t>
         </is>
       </c>
-      <c r="L698" s="21" t="inlineStr">
+      <c r="L699" s="21" t="inlineStr">
         <is>
           <t>Non-disruptive</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L698">
+  <autoFilter ref="A2:L699">
     <filterColumn colId="3" hiddenButton="0" showButton="1">
       <filters>
         <filter val="No"/>

--- a/testplan/full_rack_testplan.xlsx
+++ b/testplan/full_rack_testplan.xlsx
@@ -5580,7 +5580,7 @@
     <row r="7" hidden="1" ht="32" customHeight="1" s="33">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>TC-AFM-005</t>
+          <t>TC-AFM-005A</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -5610,7 +5610,8 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>[g02-g17 full rack, 16 Oct 13:48 UTC, helios-tests g02-g17-20261016-135436] Pending: rccl-tests not installed on any tray and no cross-domain launch configured; AMD reports the cross-domain RCCL smoke test passing - asked for their command.
+          <t>[ID renamed 21 Oct 2026] TC-AFM-005 in the BKC-26.12 plan, where it was shared with 'Failover Policy CRUD' - renumbered TC-AFM-005A, the ID its automated test already used.
+Earlier: [g02-g17 full rack, 16 Oct 13:48 UTC, helios-tests g02-g17-20261016-135436] Pending: rccl-tests not installed on any tray and no cross-domain launch configured; AMD reports the cross-domain RCCL smoke test passing - asked for their command.
 Earlier: [g02-g17 full rack, L1 rerun with sudo, 14 Oct 2026 15:11-15:35 UTC, helios-tests g02-g17-20261014-153550] Pending: rccl-tests not installed / no cross-domain launch configured. Evidence: RcclSmokeTest multi-node failed because CT15 could not open its GPUs (the other ranks were stopped at once). Pre-flight excluded: CT02/CT05 down (no SSH, BMC up); CT01 GPUs in use by another team's job (/user/hpe/dtm/mlperf-poc ... gpu-flops).
 Earlier: [g02-g17 full rack, L1, 14 Oct 2026, helios-tests g02-g17-20261014-143740 + pre-flight 134911] Not run: rccl-tests not installed and commands.rccl.cross_domain not set. Evidence RcclSmokeTest multi-node FAILED: 'invalid argument' (ranks on CT01) and 'no ROCm-capable device' (CT03+), same GPU permission cause. Run 13:49-14:37 UTC from the jump host on 15 trays: CT02/CT05 down (no ping, BMC up); CT18 excluded (black-holed ports, see TC-AFM-001). Root cause of the GPU errors: the test account tenant-hpe is not in the 'render' group, so it cannot open /dev/kfd (amd-smi: permission denied) - rerun with sudo (commands.datapath.sudo) or after adding the account to 'render'. Another HPE workload (palsd, /var/tmp/HPE sc framework) was also running.
 Earlier: 12 Oct traffic validation T4: RcclSmokeTest across 18 trays / 72 ranks from CT01; 21/21 cells incl. 1 GB, all processes exited cleanly, exit 0.</t>
@@ -8132,7 +8133,7 @@
     <row r="52" hidden="1" ht="16" customHeight="1" s="33">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>TC-AFM-048</t>
+          <t>TC-AFM-048A</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -8162,7 +8163,8 @@
       </c>
       <c r="H52" s="21" t="inlineStr">
         <is>
-          <t>[g02-g17 full rack, non-disruptive switch + AFM API, 14 Oct 2026] 1 item(s) passed (helios-tests fullrack-switch-nd-filtered, g02-g17-20261014-092828, g02-g17-20261014-170350, g02-g17-20261014-170910)
+          <t>[ID renamed 21 Oct 2026] TC-AFM-048 in the BKC-26.12 plan, where it was shared with 'Techsupport Validation (Sideband Only)' - renumbered TC-AFM-048A, the ID its automated test already used.
+Earlier: [g02-g17 full rack, non-disruptive switch + AFM API, 14 Oct 2026] 1 item(s) passed (helios-tests fullrack-switch-nd-filtered, g02-g17-20261014-092828, g02-g17-20261014-170350, g02-g17-20261014-170910)
 Earlier: CRUD + login audit events present; duplicate Delete/requestauthorization is a known WARN (AIFM-1363).</t>
         </is>
       </c>
